--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,6 +1014,2148 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120542081</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>595366</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6290181</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120542119</v>
+      </c>
+      <c r="B6" t="n">
+        <v>86371</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Strimspindling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cortinarius glaucopus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff. : Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>595309</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6290212</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120542110</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>595495</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6290196</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120542136</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>595224</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6290251</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120542115</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104945</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>595381</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6290210</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120542135</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>595263</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6290238</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120542134</v>
+      </c>
+      <c r="B11" t="n">
+        <v>104945</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>595286</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6290263</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120542138</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>595174</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6290242</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120542077</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>595300</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6290200</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120542082</v>
+      </c>
+      <c r="B14" t="n">
+        <v>94433</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>595369</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6290177</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120542133</v>
+      </c>
+      <c r="B15" t="n">
+        <v>104945</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>595380</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6290261</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120542109</v>
+      </c>
+      <c r="B16" t="n">
+        <v>109848</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>595488</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6290187</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120542117</v>
+      </c>
+      <c r="B17" t="n">
+        <v>86212</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>443</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Olivbrun spindling</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cortinarius cotoneus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>595312</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6290212</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120542101</v>
+      </c>
+      <c r="B18" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>595477</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6290162</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120542139</v>
+      </c>
+      <c r="B19" t="n">
+        <v>94433</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>595121</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6290223</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120542113</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>595474</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6290193</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120542114</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>595383</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6290202</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120542078</v>
+      </c>
+      <c r="B22" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>595323</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6290189</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120542137</v>
+      </c>
+      <c r="B23" t="n">
+        <v>86343</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>431</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Munkspindling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cortinarius coerulescentium</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Rob. Henry</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>595199</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6290236</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120542083</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79548</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>595365</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6290178</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120542112</v>
+      </c>
+      <c r="B25" t="n">
+        <v>94433</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>595494</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6290191</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120542081</v>
+        <v>120542115</v>
       </c>
       <c r="B5" t="n">
-        <v>100194</v>
+        <v>104945</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595366</v>
+        <v>595381</v>
       </c>
       <c r="R5" t="n">
-        <v>6290181</v>
+        <v>6290210</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120542119</v>
+        <v>120542133</v>
       </c>
       <c r="B6" t="n">
-        <v>86371</v>
+        <v>104945</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3624</v>
+        <v>221141</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595309</v>
+        <v>595380</v>
       </c>
       <c r="R6" t="n">
-        <v>6290212</v>
+        <v>6290261</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120542110</v>
+        <v>120542114</v>
       </c>
       <c r="B7" t="n">
         <v>100194</v>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595495</v>
+        <v>595383</v>
       </c>
       <c r="R7" t="n">
-        <v>6290196</v>
+        <v>6290202</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1322,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120542136</v>
+        <v>120542113</v>
       </c>
       <c r="B8" t="n">
         <v>100194</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595224</v>
+        <v>595474</v>
       </c>
       <c r="R8" t="n">
-        <v>6290251</v>
+        <v>6290193</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120542115</v>
+        <v>120542083</v>
       </c>
       <c r="B9" t="n">
-        <v>104945</v>
+        <v>79548</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221141</v>
+        <v>6003719</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Traslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Scytinium lichenoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595381</v>
+        <v>595365</v>
       </c>
       <c r="R9" t="n">
-        <v>6290210</v>
+        <v>6290178</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120542135</v>
+        <v>120542078</v>
       </c>
       <c r="B10" t="n">
         <v>100194</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595263</v>
+        <v>595323</v>
       </c>
       <c r="R10" t="n">
-        <v>6290238</v>
+        <v>6290189</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120542134</v>
+        <v>120542077</v>
       </c>
       <c r="B11" t="n">
-        <v>104945</v>
+        <v>100194</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595286</v>
+        <v>595300</v>
       </c>
       <c r="R11" t="n">
-        <v>6290263</v>
+        <v>6290200</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,7 +1832,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120542077</v>
+        <v>120542136</v>
       </c>
       <c r="B13" t="n">
         <v>100194</v>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595300</v>
+        <v>595224</v>
       </c>
       <c r="R13" t="n">
-        <v>6290200</v>
+        <v>6290251</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120542082</v>
+        <v>120542135</v>
       </c>
       <c r="B14" t="n">
-        <v>94433</v>
+        <v>100194</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595369</v>
+        <v>595263</v>
       </c>
       <c r="R14" t="n">
-        <v>6290177</v>
+        <v>6290238</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120542133</v>
+        <v>120542112</v>
       </c>
       <c r="B15" t="n">
-        <v>104945</v>
+        <v>94433</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2052,21 +2052,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221141</v>
+        <v>2667</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595380</v>
+        <v>595494</v>
       </c>
       <c r="R15" t="n">
-        <v>6290261</v>
+        <v>6290191</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2138,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120542109</v>
+        <v>120542101</v>
       </c>
       <c r="B16" t="n">
-        <v>109848</v>
+        <v>100194</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2154,21 +2154,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595488</v>
+        <v>595477</v>
       </c>
       <c r="R16" t="n">
-        <v>6290187</v>
+        <v>6290162</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120542117</v>
+        <v>120542081</v>
       </c>
       <c r="B17" t="n">
-        <v>86212</v>
+        <v>100194</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2252,25 +2252,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>443</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olivbrun spindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius cotoneus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595312</v>
+        <v>595366</v>
       </c>
       <c r="R17" t="n">
-        <v>6290212</v>
+        <v>6290181</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120542101</v>
+        <v>120542137</v>
       </c>
       <c r="B18" t="n">
-        <v>100194</v>
+        <v>86343</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2354,25 +2354,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>431</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Munkspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius coerulescentium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Rob. Henry</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2382,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595477</v>
+        <v>595199</v>
       </c>
       <c r="R18" t="n">
-        <v>6290162</v>
+        <v>6290236</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2412,12 +2412,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2444,10 +2444,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120542139</v>
+        <v>120542109</v>
       </c>
       <c r="B19" t="n">
-        <v>94433</v>
+        <v>109848</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2460,21 +2460,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2667</v>
+        <v>219677</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595121</v>
+        <v>595488</v>
       </c>
       <c r="R19" t="n">
-        <v>6290223</v>
+        <v>6290187</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2514,12 +2514,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2546,10 +2546,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120542113</v>
+        <v>120542082</v>
       </c>
       <c r="B20" t="n">
-        <v>100194</v>
+        <v>94433</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2562,21 +2562,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595474</v>
+        <v>595369</v>
       </c>
       <c r="R20" t="n">
-        <v>6290193</v>
+        <v>6290177</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120542114</v>
+        <v>120542139</v>
       </c>
       <c r="B21" t="n">
-        <v>100194</v>
+        <v>94433</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2664,21 +2664,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595383</v>
+        <v>595121</v>
       </c>
       <c r="R21" t="n">
-        <v>6290202</v>
+        <v>6290223</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120542078</v>
+        <v>120542119</v>
       </c>
       <c r="B22" t="n">
-        <v>100194</v>
+        <v>86371</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2766,21 +2766,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>3624</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius glaucopus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff. : Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595323</v>
+        <v>595309</v>
       </c>
       <c r="R22" t="n">
-        <v>6290189</v>
+        <v>6290212</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120542137</v>
+        <v>120542110</v>
       </c>
       <c r="B23" t="n">
-        <v>86343</v>
+        <v>100194</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2864,25 +2864,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>431</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Munkspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius coerulescentium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Rob. Henry</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2892,10 +2892,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595199</v>
+        <v>595495</v>
       </c>
       <c r="R23" t="n">
-        <v>6290236</v>
+        <v>6290196</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2922,12 +2922,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2954,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120542083</v>
+        <v>120542117</v>
       </c>
       <c r="B24" t="n">
-        <v>79548</v>
+        <v>86212</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2966,25 +2966,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6003719</v>
+        <v>443</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Olivbrun spindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Cortinarius cotoneus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595365</v>
+        <v>595312</v>
       </c>
       <c r="R24" t="n">
-        <v>6290178</v>
+        <v>6290212</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3056,10 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120542112</v>
+        <v>120542134</v>
       </c>
       <c r="B25" t="n">
-        <v>94433</v>
+        <v>104945</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3072,21 +3072,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2667</v>
+        <v>221141</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595494</v>
+        <v>595286</v>
       </c>
       <c r="R25" t="n">
-        <v>6290191</v>
+        <v>6290263</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3156,6 +3156,345 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122753749</v>
+      </c>
+      <c r="B26" t="n">
+        <v>110483</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Isgärde ost, Öl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>595493</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6290189</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>blandskog med en del grova granar, frisk mark</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Liselotte Wetterstrand Waldenström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122753994</v>
+      </c>
+      <c r="B27" t="n">
+        <v>106007</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Isgärde ost, Öl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>595493</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6290189</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Liselotte Wetterstrand Waldenström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122753750</v>
+      </c>
+      <c r="B28" t="n">
+        <v>100611</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Isgärde ost, Öl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>595493</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6290189</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>blandskog med en del grova granar, frisk mark</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Liselotte Wetterstrand Waldenström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3158,10 +3158,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122753994</v>
+        <v>122753750</v>
       </c>
       <c r="B26" t="n">
-        <v>106009</v>
+        <v>100621</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3170,30 +3170,34 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -3249,6 +3253,11 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>blandskog med en del grova granar, frisk mark</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3268,7 +3277,7 @@
         <v>122753749</v>
       </c>
       <c r="B27" t="n">
-        <v>110485</v>
+        <v>110493</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3381,10 +3390,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122753750</v>
+        <v>122753994</v>
       </c>
       <c r="B28" t="n">
-        <v>100613</v>
+        <v>106017</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3393,34 +3402,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3476,11 +3481,6 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>blandskog med en del grova granar, frisk mark</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3495,6 +3495,335 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122904417</v>
+      </c>
+      <c r="B29" t="n">
+        <v>90964</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Isgärde ost, Öl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>595176</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6290216</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>döende tall</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Liselotte Wetterstrand Waldenström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122904427</v>
+      </c>
+      <c r="B30" t="n">
+        <v>110495</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Isgärde ost, Öl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>595134</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6290239</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Liselotte Wetterstrand Waldenström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122904428</v>
+      </c>
+      <c r="B31" t="n">
+        <v>100623</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Isgärde ost, Öl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>595134</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6290239</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Liselotte Wetterstrand Waldenström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3161,7 +3161,7 @@
         <v>122753750</v>
       </c>
       <c r="B26" t="n">
-        <v>100621</v>
+        <v>100623</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>122753749</v>
       </c>
       <c r="B27" t="n">
-        <v>110493</v>
+        <v>110495</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>122753994</v>
       </c>
       <c r="B28" t="n">
-        <v>106017</v>
+        <v>106019</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3608,10 +3608,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122904427</v>
+        <v>122904428</v>
       </c>
       <c r="B30" t="n">
-        <v>110495</v>
+        <v>100623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3624,26 +3624,30 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -3715,10 +3719,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122904428</v>
+        <v>122904427</v>
       </c>
       <c r="B31" t="n">
-        <v>100623</v>
+        <v>110495</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3731,30 +3735,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3158,10 +3158,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122753750</v>
+        <v>122753749</v>
       </c>
       <c r="B26" t="n">
-        <v>100623</v>
+        <v>110503</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3174,28 +3174,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122753749</v>
+        <v>122753750</v>
       </c>
       <c r="B27" t="n">
-        <v>110495</v>
+        <v>100631</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3290,28 +3290,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -3393,7 +3393,7 @@
         <v>122753994</v>
       </c>
       <c r="B28" t="n">
-        <v>106019</v>
+        <v>106027</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122904417</v>
+        <v>122904428</v>
       </c>
       <c r="B29" t="n">
-        <v>90964</v>
+        <v>100631</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3509,30 +3509,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3540,10 +3545,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595176</v>
+        <v>595134</v>
       </c>
       <c r="R29" t="n">
-        <v>6290216</v>
+        <v>6290239</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3576,11 +3581,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>döende tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3608,10 +3608,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122904428</v>
+        <v>122904417</v>
       </c>
       <c r="B30" t="n">
-        <v>100623</v>
+        <v>90972</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3620,35 +3620,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3656,10 +3651,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595134</v>
+        <v>595176</v>
       </c>
       <c r="R30" t="n">
-        <v>6290239</v>
+        <v>6290216</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3692,6 +3687,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>döende tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3722,7 +3722,7 @@
         <v>122904427</v>
       </c>
       <c r="B31" t="n">
-        <v>110495</v>
+        <v>110503</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3274,10 +3274,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122753750</v>
+        <v>122753994</v>
       </c>
       <c r="B27" t="n">
-        <v>100631</v>
+        <v>106027</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3286,34 +3286,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3369,11 +3365,6 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>blandskog med en del grova granar, frisk mark</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3390,10 +3381,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122753994</v>
+        <v>122753750</v>
       </c>
       <c r="B28" t="n">
-        <v>106027</v>
+        <v>100631</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3402,30 +3393,34 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220785</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3481,6 +3476,11 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>blandskog med en del grova granar, frisk mark</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3497,10 +3497,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122904428</v>
+        <v>122904417</v>
       </c>
       <c r="B29" t="n">
-        <v>100631</v>
+        <v>90972</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3509,35 +3509,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3545,10 +3540,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595134</v>
+        <v>595176</v>
       </c>
       <c r="R29" t="n">
-        <v>6290239</v>
+        <v>6290216</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3581,6 +3576,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>döende tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3608,10 +3608,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122904417</v>
+        <v>122904427</v>
       </c>
       <c r="B30" t="n">
-        <v>90972</v>
+        <v>110503</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3620,30 +3620,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3651,10 +3652,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595176</v>
+        <v>595134</v>
       </c>
       <c r="R30" t="n">
-        <v>6290216</v>
+        <v>6290239</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3687,11 +3688,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>döende tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3719,10 +3715,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122904427</v>
+        <v>122904428</v>
       </c>
       <c r="B31" t="n">
-        <v>110503</v>
+        <v>100631</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3735,26 +3731,30 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3497,10 +3497,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122904417</v>
+        <v>122904427</v>
       </c>
       <c r="B29" t="n">
-        <v>90972</v>
+        <v>110503</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3509,30 +3509,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3540,10 +3541,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595176</v>
+        <v>595134</v>
       </c>
       <c r="R29" t="n">
-        <v>6290216</v>
+        <v>6290239</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3576,11 +3577,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>döende tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3608,10 +3604,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122904427</v>
+        <v>122904417</v>
       </c>
       <c r="B30" t="n">
-        <v>110503</v>
+        <v>90972</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3620,31 +3616,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3652,10 +3647,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595134</v>
+        <v>595176</v>
       </c>
       <c r="R30" t="n">
-        <v>6290239</v>
+        <v>6290216</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3688,6 +3683,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>döende tall</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3158,10 +3158,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122753749</v>
+        <v>122753994</v>
       </c>
       <c r="B26" t="n">
-        <v>110503</v>
+        <v>106027</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3170,20 +3170,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219711</v>
+        <v>220785</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3193,11 +3193,7 @@
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -3253,11 +3249,6 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>blandskog med en del grova granar, frisk mark</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3274,10 +3265,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122753994</v>
+        <v>122753750</v>
       </c>
       <c r="B27" t="n">
-        <v>106027</v>
+        <v>100631</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3286,30 +3277,34 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220785</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3365,6 +3360,11 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>blandskog med en del grova granar, frisk mark</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3381,10 +3381,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122753750</v>
+        <v>122753749</v>
       </c>
       <c r="B28" t="n">
-        <v>100631</v>
+        <v>110503</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3397,28 +3397,28 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -3604,10 +3604,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122904417</v>
+        <v>122904428</v>
       </c>
       <c r="B30" t="n">
-        <v>90972</v>
+        <v>100631</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3616,30 +3616,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3647,10 +3652,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595176</v>
+        <v>595134</v>
       </c>
       <c r="R30" t="n">
-        <v>6290216</v>
+        <v>6290239</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3683,11 +3688,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>döende tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3715,10 +3715,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122904428</v>
+        <v>122904417</v>
       </c>
       <c r="B31" t="n">
-        <v>100631</v>
+        <v>90972</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3727,35 +3727,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3763,10 +3758,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595134</v>
+        <v>595176</v>
       </c>
       <c r="R31" t="n">
-        <v>6290239</v>
+        <v>6290216</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3799,6 +3794,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>döende tall</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3604,10 +3604,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122904428</v>
+        <v>122904417</v>
       </c>
       <c r="B30" t="n">
-        <v>100631</v>
+        <v>90972</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3616,35 +3616,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3652,10 +3647,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595134</v>
+        <v>595176</v>
       </c>
       <c r="R30" t="n">
-        <v>6290239</v>
+        <v>6290216</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3688,6 +3683,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>döende tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3715,10 +3715,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122904417</v>
+        <v>122904428</v>
       </c>
       <c r="B31" t="n">
-        <v>90972</v>
+        <v>100631</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3727,30 +3727,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3758,10 +3763,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595176</v>
+        <v>595134</v>
       </c>
       <c r="R31" t="n">
-        <v>6290216</v>
+        <v>6290239</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3794,11 +3799,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>döende tall</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3158,10 +3158,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122753994</v>
+        <v>122753750</v>
       </c>
       <c r="B26" t="n">
-        <v>106027</v>
+        <v>100634</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3170,30 +3170,34 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -3249,6 +3253,11 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>blandskog med en del grova granar, frisk mark</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3265,10 +3274,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122753750</v>
+        <v>122753994</v>
       </c>
       <c r="B27" t="n">
-        <v>100631</v>
+        <v>106030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3277,34 +3286,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3360,11 +3365,6 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>blandskog med en del grova granar, frisk mark</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3384,7 +3384,7 @@
         <v>122753749</v>
       </c>
       <c r="B28" t="n">
-        <v>110503</v>
+        <v>110509</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122904427</v>
+        <v>122904417</v>
       </c>
       <c r="B29" t="n">
-        <v>110503</v>
+        <v>90975</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3509,31 +3509,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3541,10 +3540,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595134</v>
+        <v>595176</v>
       </c>
       <c r="R29" t="n">
-        <v>6290239</v>
+        <v>6290216</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3577,6 +3576,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>döende tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3604,10 +3608,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122904417</v>
+        <v>122904427</v>
       </c>
       <c r="B30" t="n">
-        <v>90972</v>
+        <v>110509</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3616,30 +3620,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3647,10 +3652,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595176</v>
+        <v>595134</v>
       </c>
       <c r="R30" t="n">
-        <v>6290216</v>
+        <v>6290239</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3683,11 +3688,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>döende tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3718,7 +3718,7 @@
         <v>122904428</v>
       </c>
       <c r="B31" t="n">
-        <v>100631</v>
+        <v>100634</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3158,10 +3158,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122753750</v>
+        <v>122753749</v>
       </c>
       <c r="B26" t="n">
-        <v>100634</v>
+        <v>110511</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3174,28 +3174,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3277,7 +3277,7 @@
         <v>122753994</v>
       </c>
       <c r="B27" t="n">
-        <v>106030</v>
+        <v>106032</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3381,10 +3381,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122753749</v>
+        <v>122753750</v>
       </c>
       <c r="B28" t="n">
-        <v>110509</v>
+        <v>100636</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3397,28 +3397,28 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122904417</v>
+        <v>122904427</v>
       </c>
       <c r="B29" t="n">
-        <v>90975</v>
+        <v>110511</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3509,30 +3509,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3540,10 +3541,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595176</v>
+        <v>595134</v>
       </c>
       <c r="R29" t="n">
-        <v>6290216</v>
+        <v>6290239</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3576,11 +3577,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>döende tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3608,10 +3604,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122904427</v>
+        <v>122904428</v>
       </c>
       <c r="B30" t="n">
-        <v>110509</v>
+        <v>100636</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3624,26 +3620,30 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -3715,10 +3715,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122904428</v>
+        <v>122904417</v>
       </c>
       <c r="B31" t="n">
-        <v>100634</v>
+        <v>90977</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3727,35 +3727,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3763,10 +3758,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595134</v>
+        <v>595176</v>
       </c>
       <c r="R31" t="n">
-        <v>6290239</v>
+        <v>6290216</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3799,6 +3794,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>döende tall</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3500,7 +3500,7 @@
         <v>122904427</v>
       </c>
       <c r="B29" t="n">
-        <v>110511</v>
+        <v>110518</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>122904428</v>
       </c>
       <c r="B30" t="n">
-        <v>100636</v>
+        <v>100642</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>122904417</v>
       </c>
       <c r="B31" t="n">
-        <v>90977</v>
+        <v>90983</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116270278</v>
+        <v>120542112</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
+        <v>94556</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,38 +921,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Galgbacken (Galgbacken), Öl</t>
+          <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595176</v>
+        <v>595494</v>
       </c>
       <c r="R4" t="n">
-        <v>6290217</v>
+        <v>6290191</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,17 +979,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120542112</v>
+        <v>120542135</v>
       </c>
       <c r="B5" t="n">
-        <v>94556</v>
+        <v>100320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595494</v>
+        <v>595263</v>
       </c>
       <c r="R5" t="n">
-        <v>6290191</v>
+        <v>6290238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,12 +1081,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120542135</v>
+        <v>120542113</v>
       </c>
       <c r="B6" t="n">
         <v>100320</v>
@@ -1158,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595263</v>
+        <v>595474</v>
       </c>
       <c r="R6" t="n">
-        <v>6290238</v>
+        <v>6290193</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,12 +1183,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120542113</v>
+        <v>120542078</v>
       </c>
       <c r="B7" t="n">
         <v>100320</v>
@@ -1260,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595474</v>
+        <v>595323</v>
       </c>
       <c r="R7" t="n">
-        <v>6290193</v>
+        <v>6290189</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120542078</v>
+        <v>120542114</v>
       </c>
       <c r="B8" t="n">
         <v>100320</v>
@@ -1362,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595323</v>
+        <v>595383</v>
       </c>
       <c r="R8" t="n">
-        <v>6290189</v>
+        <v>6290202</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120542138</v>
+        <v>120542077</v>
       </c>
       <c r="B9" t="n">
         <v>100320</v>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595174</v>
+        <v>595300</v>
       </c>
       <c r="R9" t="n">
-        <v>6290242</v>
+        <v>6290200</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,12 +1489,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120542114</v>
+        <v>120542117</v>
       </c>
       <c r="B10" t="n">
-        <v>100320</v>
+        <v>86015</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1538,25 +1533,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>443</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Olivbrun spindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius cotoneus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595383</v>
+        <v>595312</v>
       </c>
       <c r="R10" t="n">
-        <v>6290202</v>
+        <v>6290212</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120542077</v>
+        <v>120542101</v>
       </c>
       <c r="B11" t="n">
         <v>100320</v>
@@ -1668,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595300</v>
+        <v>595477</v>
       </c>
       <c r="R11" t="n">
-        <v>6290200</v>
+        <v>6290162</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120542117</v>
+        <v>120542136</v>
       </c>
       <c r="B12" t="n">
-        <v>86015</v>
+        <v>100320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1742,25 +1737,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>443</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olivbrun spindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius cotoneus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595312</v>
+        <v>595224</v>
       </c>
       <c r="R12" t="n">
-        <v>6290212</v>
+        <v>6290251</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,12 +1795,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120542101</v>
+        <v>120542083</v>
       </c>
       <c r="B13" t="n">
-        <v>100320</v>
+        <v>79600</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>6003719</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Traslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scytinium lichenoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595477</v>
+        <v>595365</v>
       </c>
       <c r="R13" t="n">
-        <v>6290162</v>
+        <v>6290178</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120542136</v>
+        <v>120542133</v>
       </c>
       <c r="B14" t="n">
-        <v>100320</v>
+        <v>105072</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595224</v>
+        <v>595380</v>
       </c>
       <c r="R14" t="n">
-        <v>6290251</v>
+        <v>6290261</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120542083</v>
+        <v>120542109</v>
       </c>
       <c r="B15" t="n">
-        <v>79600</v>
+        <v>109978</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2052,21 +2047,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6003719</v>
+        <v>219677</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595365</v>
+        <v>595488</v>
       </c>
       <c r="R15" t="n">
-        <v>6290178</v>
+        <v>6290187</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120542133</v>
+        <v>120542081</v>
       </c>
       <c r="B16" t="n">
-        <v>105072</v>
+        <v>100320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2154,21 +2149,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595380</v>
+        <v>595366</v>
       </c>
       <c r="R16" t="n">
-        <v>6290261</v>
+        <v>6290181</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2208,12 +2203,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2240,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120542109</v>
+        <v>120542119</v>
       </c>
       <c r="B17" t="n">
-        <v>109978</v>
+        <v>86176</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2256,21 +2251,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219677</v>
+        <v>3624</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Cortinarius glaucopus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff. : Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595488</v>
+        <v>595309</v>
       </c>
       <c r="R17" t="n">
-        <v>6290187</v>
+        <v>6290212</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120542081</v>
+        <v>120542082</v>
       </c>
       <c r="B18" t="n">
-        <v>100320</v>
+        <v>94556</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2358,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2382,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595366</v>
+        <v>595369</v>
       </c>
       <c r="R18" t="n">
-        <v>6290181</v>
+        <v>6290177</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2444,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120542137</v>
+        <v>120542115</v>
       </c>
       <c r="B19" t="n">
-        <v>86148</v>
+        <v>105072</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2456,25 +2451,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>431</v>
+        <v>221141</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Munkspindling</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius coerulescentium</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Rob. Henry</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2484,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595199</v>
+        <v>595381</v>
       </c>
       <c r="R19" t="n">
-        <v>6290236</v>
+        <v>6290210</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2514,12 +2509,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2546,10 +2541,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120542119</v>
+        <v>120542110</v>
       </c>
       <c r="B20" t="n">
-        <v>86176</v>
+        <v>100320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2562,21 +2557,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3624</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2586,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595309</v>
+        <v>595495</v>
       </c>
       <c r="R20" t="n">
-        <v>6290212</v>
+        <v>6290196</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2648,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120542139</v>
+        <v>120542134</v>
       </c>
       <c r="B21" t="n">
-        <v>94556</v>
+        <v>105072</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2664,21 +2659,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2667</v>
+        <v>221141</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2688,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595121</v>
+        <v>595286</v>
       </c>
       <c r="R21" t="n">
-        <v>6290223</v>
+        <v>6290263</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,10 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120542082</v>
+        <v>122753749</v>
       </c>
       <c r="B22" t="n">
-        <v>94556</v>
+        <v>110511</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2766,37 +2761,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2667</v>
+        <v>219711</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Isgärde, Öl</t>
+          <t>Isgärde ost, Öl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595369</v>
+        <v>595493</v>
       </c>
       <c r="R22" t="n">
-        <v>6290177</v>
+        <v>6290189</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2820,12 +2823,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2834,28 +2837,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>blandskog med en del grova granar, frisk mark</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Ulla-Britt Andersson, Liselotte Wetterstrand Waldenström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120542115</v>
+        <v>122753994</v>
       </c>
       <c r="B23" t="n">
-        <v>105072</v>
+        <v>106032</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2864,20 +2873,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221141</v>
+        <v>220785</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2886,19 +2895,23 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Isgärde, Öl</t>
+          <t>Isgärde ost, Öl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595381</v>
+        <v>595493</v>
       </c>
       <c r="R23" t="n">
-        <v>6290210</v>
+        <v>6290189</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2922,12 +2935,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2936,28 +2949,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Ulla-Britt Andersson, Liselotte Wetterstrand Waldenström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120542110</v>
+        <v>122753750</v>
       </c>
       <c r="B24" t="n">
-        <v>100320</v>
+        <v>100636</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2988,19 +3002,27 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Isgärde, Öl</t>
+          <t>Isgärde ost, Öl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595495</v>
+        <v>595493</v>
       </c>
       <c r="R24" t="n">
-        <v>6290196</v>
+        <v>6290189</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3024,12 +3046,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3038,791 +3060,27 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>blandskog med en del grova granar, frisk mark</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Ulla-Britt Andersson, Liselotte Wetterstrand Waldenström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>120542134</v>
-      </c>
-      <c r="B25" t="n">
-        <v>105072</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>221141</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Gullviva</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Primula veris</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Isgärde, Öl</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>595286</v>
-      </c>
-      <c r="R25" t="n">
-        <v>6290263</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Mörbylånga</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Öland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Glömminge</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2024-10-14</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2024-10-14</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Patrik Celander</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Patrik Celander</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>122753749</v>
-      </c>
-      <c r="B26" t="n">
-        <v>110511</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>219711</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Sårläka</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Sanicula europaea</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Isgärde ost, Öl</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>595493</v>
-      </c>
-      <c r="R26" t="n">
-        <v>6290189</v>
-      </c>
-      <c r="S26" t="n">
-        <v>25</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Mörbylånga</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Öland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Glömminge</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>blandskog med en del grova granar, frisk mark</t>
-        </is>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Ulla-Britt Andersson, Liselotte Wetterstrand Waldenström</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>122753994</v>
-      </c>
-      <c r="B27" t="n">
-        <v>106032</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>220785</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Isgärde ost, Öl</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>595493</v>
-      </c>
-      <c r="R27" t="n">
-        <v>6290189</v>
-      </c>
-      <c r="S27" t="n">
-        <v>25</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Mörbylånga</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Öland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Glömminge</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Ulla-Britt Andersson, Liselotte Wetterstrand Waldenström</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>122753750</v>
-      </c>
-      <c r="B28" t="n">
-        <v>100636</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Isgärde ost, Öl</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>595493</v>
-      </c>
-      <c r="R28" t="n">
-        <v>6290189</v>
-      </c>
-      <c r="S28" t="n">
-        <v>25</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Mörbylånga</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Öland</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Glömminge</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>blandskog med en del grova granar, frisk mark</t>
-        </is>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Ulla-Britt Andersson, Liselotte Wetterstrand Waldenström</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>122904427</v>
-      </c>
-      <c r="B29" t="n">
-        <v>110521</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>219711</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Sårläka</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Sanicula europaea</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Isgärde ost, Öl</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>595134</v>
-      </c>
-      <c r="R29" t="n">
-        <v>6290239</v>
-      </c>
-      <c r="S29" t="n">
-        <v>25</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Mörbylånga</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Öland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Glömminge</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Ulla-Britt Andersson, Liselotte Wetterstrand Waldenström</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>122904417</v>
-      </c>
-      <c r="B30" t="n">
-        <v>90986</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Isgärde ost, Öl</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>595176</v>
-      </c>
-      <c r="R30" t="n">
-        <v>6290216</v>
-      </c>
-      <c r="S30" t="n">
-        <v>25</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Mörbylånga</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Öland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Glömminge</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>döende tall</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Ulla-Britt Andersson, Liselotte Wetterstrand Waldenström</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>122904428</v>
-      </c>
-      <c r="B31" t="n">
-        <v>100645</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Isgärde ost, Öl</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>595134</v>
-      </c>
-      <c r="R31" t="n">
-        <v>6290239</v>
-      </c>
-      <c r="S31" t="n">
-        <v>25</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Mörbylånga</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Öland</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Glömminge</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Ulla-Britt Andersson, Liselotte Wetterstrand Waldenström</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3082,6 +3082,4734 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127736872</v>
+      </c>
+      <c r="B25" t="n">
+        <v>105400</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>595265</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6290208</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127736831</v>
+      </c>
+      <c r="B26" t="n">
+        <v>105400</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>595286</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6290259</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127736867</v>
+      </c>
+      <c r="B27" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>595320</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6290206</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127736857</v>
+      </c>
+      <c r="B28" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>595446</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6290169</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127736860</v>
+      </c>
+      <c r="B29" t="n">
+        <v>105400</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>595397</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6290188</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127736844</v>
+      </c>
+      <c r="B30" t="n">
+        <v>105400</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>595448</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6290238</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127736859</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98368</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>595396</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6290183</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127736842</v>
+      </c>
+      <c r="B32" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>595442</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6290205</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127736721</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98428</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>595296</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6290259</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127736848</v>
+      </c>
+      <c r="B34" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>595470</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6290237</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127736851</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98472</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>595488</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6290180</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127736715</v>
+      </c>
+      <c r="B36" t="n">
+        <v>95530</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2676</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grov baronmossa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Anomodon viticulosus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>595213</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6290222</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127736719</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98428</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>595245</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6290215</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127736861</v>
+      </c>
+      <c r="B38" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>595396</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6290191</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127736724</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98425</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>595326</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6290257</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127736832</v>
+      </c>
+      <c r="B40" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>595287</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6290259</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127736855</v>
+      </c>
+      <c r="B41" t="n">
+        <v>110544</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>595472</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6290168</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127736836</v>
+      </c>
+      <c r="B42" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>595321</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6290251</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127736827</v>
+      </c>
+      <c r="B43" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>595214</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6290272</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127736725</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98428</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>595345</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6290259</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127736874</v>
+      </c>
+      <c r="B45" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>595234</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6290231</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127736737</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98428</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>595256</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6290277</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127736846</v>
+      </c>
+      <c r="B47" t="n">
+        <v>110544</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>595473</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6290238</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127736720</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98428</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>595305</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6290257</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127736858</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>595407</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6290191</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127736852</v>
+      </c>
+      <c r="B50" t="n">
+        <v>105400</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>595490</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6290176</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127736723</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98428</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>595311</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6290257</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127736736</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98428</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>595312</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6290265</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127736833</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98472</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>595294</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6290260</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127736871</v>
+      </c>
+      <c r="B54" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>595263</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6290211</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127736727</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98428</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>595482</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6290215</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127736717</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98428</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>595312</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6290198</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127736866</v>
+      </c>
+      <c r="B57" t="n">
+        <v>110544</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>595318</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6290207</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127736826</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98367</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>595215</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6290279</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127736726</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98428</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>595419</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6290207</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127736840</v>
+      </c>
+      <c r="B60" t="n">
+        <v>105400</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>595387</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6290227</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127736835</v>
+      </c>
+      <c r="B61" t="n">
+        <v>105400</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>595320</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6290253</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127736856</v>
+      </c>
+      <c r="B62" t="n">
+        <v>105400</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>595446</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6290169</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127736800</v>
+      </c>
+      <c r="B63" t="n">
+        <v>105400</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>595399</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6290260</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127736854</v>
+      </c>
+      <c r="B64" t="n">
+        <v>102954</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>595486</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6290171</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127736716</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98428</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>595320</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6290193</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>127736838</v>
+      </c>
+      <c r="B66" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>595371</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6290254</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127736870</v>
+      </c>
+      <c r="B67" t="n">
+        <v>110544</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>595272</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6290205</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127736853</v>
+      </c>
+      <c r="B68" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>595491</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6290172</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127736865</v>
+      </c>
+      <c r="B69" t="n">
+        <v>105400</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>595335</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6290212</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>127736863</v>
+      </c>
+      <c r="B70" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>595354</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6290194</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>127736837</v>
+      </c>
+      <c r="B71" t="n">
+        <v>105400</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>595371</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6290254</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>127736718</v>
+      </c>
+      <c r="B72" t="n">
+        <v>98428</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>595293</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6290204</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3084,10 +3084,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127736872</v>
+        <v>127736867</v>
       </c>
       <c r="B25" t="n">
-        <v>105400</v>
+        <v>100632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3095,21 +3095,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595265</v>
+        <v>595320</v>
       </c>
       <c r="R25" t="n">
-        <v>6290208</v>
+        <v>6290206</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,7 +3181,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127736831</v>
+        <v>127736872</v>
       </c>
       <c r="B26" t="n">
         <v>105400</v>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595286</v>
+        <v>595265</v>
       </c>
       <c r="R26" t="n">
-        <v>6290259</v>
+        <v>6290208</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3278,10 +3278,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127736867</v>
+        <v>127736831</v>
       </c>
       <c r="B27" t="n">
-        <v>100632</v>
+        <v>105400</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3289,21 +3289,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595320</v>
+        <v>595286</v>
       </c>
       <c r="R27" t="n">
-        <v>6290206</v>
+        <v>6290259</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,10 +3375,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127736857</v>
+        <v>127736860</v>
       </c>
       <c r="B28" t="n">
-        <v>100632</v>
+        <v>105400</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3386,21 +3386,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595446</v>
+        <v>595397</v>
       </c>
       <c r="R28" t="n">
-        <v>6290169</v>
+        <v>6290188</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127736860</v>
+        <v>127736857</v>
       </c>
       <c r="B29" t="n">
-        <v>105400</v>
+        <v>100632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3483,21 +3483,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595397</v>
+        <v>595446</v>
       </c>
       <c r="R29" t="n">
-        <v>6290188</v>
+        <v>6290169</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127736842</v>
+        <v>127736721</v>
       </c>
       <c r="B32" t="n">
-        <v>100632</v>
+        <v>98428</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3778,34 +3778,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>595442</v>
+        <v>595296</v>
       </c>
       <c r="R32" t="n">
-        <v>6290205</v>
+        <v>6290259</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3832,12 +3836,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3864,10 +3868,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127736721</v>
+        <v>127736842</v>
       </c>
       <c r="B33" t="n">
-        <v>98428</v>
+        <v>100632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3875,38 +3879,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>595296</v>
+        <v>595442</v>
       </c>
       <c r="R33" t="n">
-        <v>6290259</v>
+        <v>6290205</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3933,12 +3933,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3965,10 +3965,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127736848</v>
+        <v>127736715</v>
       </c>
       <c r="B34" t="n">
-        <v>100632</v>
+        <v>95530</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,21 +3976,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>2676</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>595470</v>
+        <v>595213</v>
       </c>
       <c r="R34" t="n">
-        <v>6290237</v>
+        <v>6290222</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4062,10 +4062,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127736851</v>
+        <v>127736848</v>
       </c>
       <c r="B35" t="n">
-        <v>98472</v>
+        <v>100632</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4073,38 +4073,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595488</v>
+        <v>595470</v>
       </c>
       <c r="R35" t="n">
-        <v>6290180</v>
+        <v>6290237</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4163,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127736715</v>
+        <v>127736861</v>
       </c>
       <c r="B36" t="n">
-        <v>95530</v>
+        <v>100632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4174,21 +4170,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2676</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4198,10 +4194,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595213</v>
+        <v>595396</v>
       </c>
       <c r="R36" t="n">
-        <v>6290222</v>
+        <v>6290191</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4228,12 +4224,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4260,10 +4256,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127736719</v>
+        <v>127736851</v>
       </c>
       <c r="B37" t="n">
-        <v>98428</v>
+        <v>98472</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4271,21 +4267,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4299,10 +4295,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595245</v>
+        <v>595488</v>
       </c>
       <c r="R37" t="n">
-        <v>6290215</v>
+        <v>6290180</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4329,12 +4325,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4361,10 +4357,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127736861</v>
+        <v>127736719</v>
       </c>
       <c r="B38" t="n">
-        <v>100632</v>
+        <v>98428</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4372,34 +4368,38 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>595396</v>
+        <v>595245</v>
       </c>
       <c r="R38" t="n">
-        <v>6290191</v>
+        <v>6290215</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4458,10 +4458,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127736724</v>
+        <v>127736832</v>
       </c>
       <c r="B39" t="n">
-        <v>98425</v>
+        <v>100632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4469,38 +4469,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219797</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>595326</v>
+        <v>595287</v>
       </c>
       <c r="R39" t="n">
-        <v>6290257</v>
+        <v>6290259</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4527,12 +4523,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4559,10 +4555,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127736832</v>
+        <v>127736724</v>
       </c>
       <c r="B40" t="n">
-        <v>100632</v>
+        <v>98425</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4570,34 +4566,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>219797</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>595287</v>
+        <v>595326</v>
       </c>
       <c r="R40" t="n">
-        <v>6290259</v>
+        <v>6290257</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4656,10 +4656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127736855</v>
+        <v>127736836</v>
       </c>
       <c r="B41" t="n">
-        <v>110544</v>
+        <v>100632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4667,21 +4667,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>595472</v>
+        <v>595321</v>
       </c>
       <c r="R41" t="n">
-        <v>6290168</v>
+        <v>6290251</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4753,7 +4753,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127736836</v>
+        <v>127736827</v>
       </c>
       <c r="B42" t="n">
         <v>100632</v>
@@ -4788,10 +4788,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>595321</v>
+        <v>595214</v>
       </c>
       <c r="R42" t="n">
-        <v>6290251</v>
+        <v>6290272</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4850,10 +4850,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127736827</v>
+        <v>127736855</v>
       </c>
       <c r="B43" t="n">
-        <v>100632</v>
+        <v>110544</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4861,21 +4861,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>595214</v>
+        <v>595472</v>
       </c>
       <c r="R43" t="n">
-        <v>6290272</v>
+        <v>6290168</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5444,10 +5444,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127736858</v>
+        <v>127736852</v>
       </c>
       <c r="B49" t="n">
-        <v>98473</v>
+        <v>105400</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5455,38 +5455,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219847</v>
+        <v>221141</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>595407</v>
+        <v>595490</v>
       </c>
       <c r="R49" t="n">
-        <v>6290191</v>
+        <v>6290176</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5545,10 +5541,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127736852</v>
+        <v>127736858</v>
       </c>
       <c r="B50" t="n">
-        <v>105400</v>
+        <v>98473</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5556,34 +5552,38 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221141</v>
+        <v>219847</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>595490</v>
+        <v>595407</v>
       </c>
       <c r="R50" t="n">
-        <v>6290176</v>
+        <v>6290191</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7028,10 +7028,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127736716</v>
+        <v>127736838</v>
       </c>
       <c r="B65" t="n">
-        <v>98428</v>
+        <v>100632</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7039,38 +7039,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>595320</v>
+        <v>595371</v>
       </c>
       <c r="R65" t="n">
-        <v>6290193</v>
+        <v>6290254</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7097,12 +7093,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7129,10 +7125,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127736838</v>
+        <v>127736716</v>
       </c>
       <c r="B66" t="n">
-        <v>100632</v>
+        <v>98428</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7140,34 +7136,38 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>595371</v>
+        <v>595320</v>
       </c>
       <c r="R66" t="n">
-        <v>6290254</v>
+        <v>6290193</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7194,12 +7194,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7226,10 +7226,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127736870</v>
+        <v>127736853</v>
       </c>
       <c r="B67" t="n">
-        <v>110544</v>
+        <v>100632</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7237,21 +7237,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7261,10 +7261,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>595272</v>
+        <v>595491</v>
       </c>
       <c r="R67" t="n">
-        <v>6290205</v>
+        <v>6290172</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7323,10 +7323,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127736853</v>
+        <v>127736870</v>
       </c>
       <c r="B68" t="n">
-        <v>100632</v>
+        <v>110544</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7334,21 +7334,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7358,10 +7358,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>595491</v>
+        <v>595272</v>
       </c>
       <c r="R68" t="n">
-        <v>6290172</v>
+        <v>6290205</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127736865</v>
+        <v>127736718</v>
       </c>
       <c r="B69" t="n">
-        <v>105400</v>
+        <v>98428</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7431,34 +7431,38 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221141</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>595335</v>
+        <v>595293</v>
       </c>
       <c r="R69" t="n">
-        <v>6290212</v>
+        <v>6290204</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7485,12 +7489,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7517,10 +7521,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127736863</v>
+        <v>127736865</v>
       </c>
       <c r="B70" t="n">
-        <v>100632</v>
+        <v>105400</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7528,21 +7532,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7552,10 +7556,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>595354</v>
+        <v>595335</v>
       </c>
       <c r="R70" t="n">
-        <v>6290194</v>
+        <v>6290212</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7711,10 +7715,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127736718</v>
+        <v>127736863</v>
       </c>
       <c r="B72" t="n">
-        <v>98428</v>
+        <v>100632</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7722,38 +7726,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>595293</v>
+        <v>595354</v>
       </c>
       <c r="R72" t="n">
-        <v>6290204</v>
+        <v>6290194</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7780,12 +7780,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3084,10 +3084,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127736867</v>
+        <v>127736872</v>
       </c>
       <c r="B25" t="n">
-        <v>100632</v>
+        <v>105400</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3095,21 +3095,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595320</v>
+        <v>595265</v>
       </c>
       <c r="R25" t="n">
-        <v>6290206</v>
+        <v>6290208</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,7 +3181,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127736872</v>
+        <v>127736831</v>
       </c>
       <c r="B26" t="n">
         <v>105400</v>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595265</v>
+        <v>595286</v>
       </c>
       <c r="R26" t="n">
-        <v>6290208</v>
+        <v>6290259</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3278,10 +3278,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127736831</v>
+        <v>127736867</v>
       </c>
       <c r="B27" t="n">
-        <v>105400</v>
+        <v>100632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3289,21 +3289,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595286</v>
+        <v>595320</v>
       </c>
       <c r="R27" t="n">
-        <v>6290259</v>
+        <v>6290206</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127736721</v>
+        <v>127736842</v>
       </c>
       <c r="B32" t="n">
-        <v>98428</v>
+        <v>100632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3778,38 +3778,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>595296</v>
+        <v>595442</v>
       </c>
       <c r="R32" t="n">
-        <v>6290259</v>
+        <v>6290205</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3836,12 +3832,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3868,10 +3864,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127736842</v>
+        <v>127736721</v>
       </c>
       <c r="B33" t="n">
-        <v>100632</v>
+        <v>98428</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,34 +3875,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>595442</v>
+        <v>595296</v>
       </c>
       <c r="R33" t="n">
-        <v>6290205</v>
+        <v>6290259</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3933,12 +3933,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -7420,10 +7420,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127736718</v>
+        <v>127736865</v>
       </c>
       <c r="B69" t="n">
-        <v>98428</v>
+        <v>105400</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7431,38 +7431,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>221141</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>595293</v>
+        <v>595335</v>
       </c>
       <c r="R69" t="n">
-        <v>6290204</v>
+        <v>6290212</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7489,12 +7485,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7521,7 +7517,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127736865</v>
+        <v>127736837</v>
       </c>
       <c r="B70" t="n">
         <v>105400</v>
@@ -7556,10 +7552,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>595335</v>
+        <v>595371</v>
       </c>
       <c r="R70" t="n">
-        <v>6290212</v>
+        <v>6290254</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7618,10 +7614,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127736837</v>
+        <v>127736863</v>
       </c>
       <c r="B71" t="n">
-        <v>105400</v>
+        <v>100632</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7629,21 +7625,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7653,10 +7649,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>595371</v>
+        <v>595354</v>
       </c>
       <c r="R71" t="n">
-        <v>6290254</v>
+        <v>6290194</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7715,10 +7711,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127736863</v>
+        <v>127736718</v>
       </c>
       <c r="B72" t="n">
-        <v>100632</v>
+        <v>98428</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7726,34 +7722,38 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>595354</v>
+        <v>595293</v>
       </c>
       <c r="R72" t="n">
-        <v>6290194</v>
+        <v>6290204</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7780,12 +7780,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3084,10 +3084,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127736872</v>
+        <v>127736867</v>
       </c>
       <c r="B25" t="n">
-        <v>105400</v>
+        <v>100632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3095,21 +3095,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595265</v>
+        <v>595320</v>
       </c>
       <c r="R25" t="n">
-        <v>6290208</v>
+        <v>6290206</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,7 +3181,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127736831</v>
+        <v>127736872</v>
       </c>
       <c r="B26" t="n">
         <v>105400</v>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595286</v>
+        <v>595265</v>
       </c>
       <c r="R26" t="n">
-        <v>6290259</v>
+        <v>6290208</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3278,10 +3278,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127736867</v>
+        <v>127736831</v>
       </c>
       <c r="B27" t="n">
-        <v>100632</v>
+        <v>105400</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3289,21 +3289,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595320</v>
+        <v>595286</v>
       </c>
       <c r="R27" t="n">
-        <v>6290206</v>
+        <v>6290259</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,10 +3375,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127736860</v>
+        <v>127736857</v>
       </c>
       <c r="B28" t="n">
-        <v>105400</v>
+        <v>100632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3386,21 +3386,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595397</v>
+        <v>595446</v>
       </c>
       <c r="R28" t="n">
-        <v>6290188</v>
+        <v>6290169</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127736857</v>
+        <v>127736860</v>
       </c>
       <c r="B29" t="n">
-        <v>100632</v>
+        <v>105400</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3483,21 +3483,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595446</v>
+        <v>595397</v>
       </c>
       <c r="R29" t="n">
-        <v>6290169</v>
+        <v>6290188</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127736842</v>
+        <v>127736721</v>
       </c>
       <c r="B32" t="n">
-        <v>100632</v>
+        <v>98428</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3778,34 +3778,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>595442</v>
+        <v>595296</v>
       </c>
       <c r="R32" t="n">
-        <v>6290205</v>
+        <v>6290259</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3832,12 +3836,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3864,10 +3868,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127736721</v>
+        <v>127736842</v>
       </c>
       <c r="B33" t="n">
-        <v>98428</v>
+        <v>100632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3875,38 +3879,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>595296</v>
+        <v>595442</v>
       </c>
       <c r="R33" t="n">
-        <v>6290259</v>
+        <v>6290205</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3933,12 +3933,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4062,10 +4062,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127736848</v>
+        <v>127736851</v>
       </c>
       <c r="B35" t="n">
-        <v>100632</v>
+        <v>98472</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4073,34 +4073,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595470</v>
+        <v>595488</v>
       </c>
       <c r="R35" t="n">
-        <v>6290237</v>
+        <v>6290180</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4159,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127736861</v>
+        <v>127736719</v>
       </c>
       <c r="B36" t="n">
-        <v>100632</v>
+        <v>98428</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4170,34 +4174,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595396</v>
+        <v>595245</v>
       </c>
       <c r="R36" t="n">
-        <v>6290191</v>
+        <v>6290215</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4224,12 +4232,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4256,10 +4264,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127736851</v>
+        <v>127736848</v>
       </c>
       <c r="B37" t="n">
-        <v>98472</v>
+        <v>100632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4267,38 +4275,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595488</v>
+        <v>595470</v>
       </c>
       <c r="R37" t="n">
-        <v>6290180</v>
+        <v>6290237</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4357,10 +4361,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127736719</v>
+        <v>127736861</v>
       </c>
       <c r="B38" t="n">
-        <v>98428</v>
+        <v>100632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4368,38 +4372,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>595245</v>
+        <v>595396</v>
       </c>
       <c r="R38" t="n">
-        <v>6290215</v>
+        <v>6290191</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4656,10 +4656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127736836</v>
+        <v>127736855</v>
       </c>
       <c r="B41" t="n">
-        <v>100632</v>
+        <v>110544</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4667,21 +4667,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>595321</v>
+        <v>595472</v>
       </c>
       <c r="R41" t="n">
-        <v>6290251</v>
+        <v>6290168</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4753,10 +4753,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127736827</v>
+        <v>127736725</v>
       </c>
       <c r="B42" t="n">
-        <v>100632</v>
+        <v>98428</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4764,34 +4764,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>595214</v>
+        <v>595345</v>
       </c>
       <c r="R42" t="n">
-        <v>6290272</v>
+        <v>6290259</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4818,12 +4822,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4850,10 +4854,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127736855</v>
+        <v>127736836</v>
       </c>
       <c r="B43" t="n">
-        <v>110544</v>
+        <v>100632</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4861,21 +4865,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4885,10 +4889,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>595472</v>
+        <v>595321</v>
       </c>
       <c r="R43" t="n">
-        <v>6290168</v>
+        <v>6290251</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4947,10 +4951,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127736725</v>
+        <v>127736827</v>
       </c>
       <c r="B44" t="n">
-        <v>98428</v>
+        <v>100632</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4958,38 +4962,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>595345</v>
+        <v>595214</v>
       </c>
       <c r="R44" t="n">
-        <v>6290259</v>
+        <v>6290272</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5016,12 +5016,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5048,10 +5048,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127736874</v>
+        <v>127736846</v>
       </c>
       <c r="B45" t="n">
-        <v>100632</v>
+        <v>110544</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5059,21 +5059,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5083,10 +5083,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>595234</v>
+        <v>595473</v>
       </c>
       <c r="R45" t="n">
-        <v>6290231</v>
+        <v>6290238</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5246,10 +5246,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127736846</v>
+        <v>127736720</v>
       </c>
       <c r="B47" t="n">
-        <v>110544</v>
+        <v>98428</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5257,34 +5257,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>595473</v>
+        <v>595305</v>
       </c>
       <c r="R47" t="n">
-        <v>6290238</v>
+        <v>6290257</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5311,12 +5315,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5343,10 +5347,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127736720</v>
+        <v>127736874</v>
       </c>
       <c r="B48" t="n">
-        <v>98428</v>
+        <v>100632</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5354,38 +5358,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>595305</v>
+        <v>595234</v>
       </c>
       <c r="R48" t="n">
-        <v>6290257</v>
+        <v>6290231</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5444,10 +5444,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127736852</v>
+        <v>127736858</v>
       </c>
       <c r="B49" t="n">
-        <v>105400</v>
+        <v>98473</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5455,34 +5455,38 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221141</v>
+        <v>219847</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>595490</v>
+        <v>595407</v>
       </c>
       <c r="R49" t="n">
-        <v>6290176</v>
+        <v>6290191</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5541,10 +5545,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127736858</v>
+        <v>127736852</v>
       </c>
       <c r="B50" t="n">
-        <v>98473</v>
+        <v>105400</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5552,38 +5556,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219847</v>
+        <v>221141</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>595407</v>
+        <v>595490</v>
       </c>
       <c r="R50" t="n">
-        <v>6290191</v>
+        <v>6290176</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6042,10 +6042,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127736727</v>
+        <v>127736866</v>
       </c>
       <c r="B55" t="n">
-        <v>98428</v>
+        <v>110544</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6053,38 +6053,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>595482</v>
+        <v>595318</v>
       </c>
       <c r="R55" t="n">
-        <v>6290215</v>
+        <v>6290207</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6111,12 +6107,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6143,7 +6139,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127736717</v>
+        <v>127736727</v>
       </c>
       <c r="B56" t="n">
         <v>98428</v>
@@ -6173,7 +6169,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6182,10 +6178,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>595312</v>
+        <v>595482</v>
       </c>
       <c r="R56" t="n">
-        <v>6290198</v>
+        <v>6290215</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6244,10 +6240,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127736866</v>
+        <v>127736717</v>
       </c>
       <c r="B57" t="n">
-        <v>110544</v>
+        <v>98428</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6255,34 +6251,38 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>595318</v>
+        <v>595312</v>
       </c>
       <c r="R57" t="n">
-        <v>6290207</v>
+        <v>6290198</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6309,12 +6309,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6543,10 +6543,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127736840</v>
+        <v>127736854</v>
       </c>
       <c r="B60" t="n">
-        <v>105400</v>
+        <v>102954</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6554,16 +6554,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221141</v>
+        <v>222002</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>595387</v>
+        <v>595486</v>
       </c>
       <c r="R60" t="n">
-        <v>6290227</v>
+        <v>6290171</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6737,7 +6737,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127736856</v>
+        <v>127736800</v>
       </c>
       <c r="B62" t="n">
         <v>105400</v>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>595446</v>
+        <v>595399</v>
       </c>
       <c r="R62" t="n">
-        <v>6290169</v>
+        <v>6290260</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6834,7 +6834,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127736800</v>
+        <v>127736840</v>
       </c>
       <c r="B63" t="n">
         <v>105400</v>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>595399</v>
+        <v>595387</v>
       </c>
       <c r="R63" t="n">
-        <v>6290260</v>
+        <v>6290227</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6931,10 +6931,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127736854</v>
+        <v>127736856</v>
       </c>
       <c r="B64" t="n">
-        <v>102954</v>
+        <v>105400</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6942,16 +6942,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222002</v>
+        <v>221141</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>595486</v>
+        <v>595446</v>
       </c>
       <c r="R64" t="n">
-        <v>6290171</v>
+        <v>6290169</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7028,10 +7028,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127736838</v>
+        <v>127736716</v>
       </c>
       <c r="B65" t="n">
-        <v>100632</v>
+        <v>98428</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7039,34 +7039,38 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>595371</v>
+        <v>595320</v>
       </c>
       <c r="R65" t="n">
-        <v>6290254</v>
+        <v>6290193</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7093,12 +7097,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7125,10 +7129,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127736716</v>
+        <v>127736838</v>
       </c>
       <c r="B66" t="n">
-        <v>98428</v>
+        <v>100632</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7136,38 +7140,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>595320</v>
+        <v>595371</v>
       </c>
       <c r="R66" t="n">
-        <v>6290193</v>
+        <v>6290254</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7194,12 +7194,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7420,10 +7420,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127736865</v>
+        <v>127736718</v>
       </c>
       <c r="B69" t="n">
-        <v>105400</v>
+        <v>98428</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7431,34 +7431,38 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221141</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>595335</v>
+        <v>595293</v>
       </c>
       <c r="R69" t="n">
-        <v>6290212</v>
+        <v>6290204</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7485,12 +7489,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7711,10 +7715,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127736718</v>
+        <v>127736865</v>
       </c>
       <c r="B72" t="n">
-        <v>98428</v>
+        <v>105400</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7722,38 +7726,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219798</v>
+        <v>221141</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>595293</v>
+        <v>595335</v>
       </c>
       <c r="R72" t="n">
-        <v>6290204</v>
+        <v>6290212</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7780,12 +7780,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3084,10 +3084,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127736867</v>
+        <v>127736872</v>
       </c>
       <c r="B25" t="n">
-        <v>100632</v>
+        <v>105406</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3095,21 +3095,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595320</v>
+        <v>595265</v>
       </c>
       <c r="R25" t="n">
-        <v>6290206</v>
+        <v>6290208</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,10 +3181,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127736872</v>
+        <v>127736831</v>
       </c>
       <c r="B26" t="n">
-        <v>105400</v>
+        <v>105406</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595265</v>
+        <v>595286</v>
       </c>
       <c r="R26" t="n">
-        <v>6290208</v>
+        <v>6290259</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3278,10 +3278,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127736831</v>
+        <v>127736867</v>
       </c>
       <c r="B27" t="n">
-        <v>105400</v>
+        <v>100638</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3289,21 +3289,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595286</v>
+        <v>595320</v>
       </c>
       <c r="R27" t="n">
-        <v>6290259</v>
+        <v>6290206</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,10 +3375,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127736857</v>
+        <v>127736860</v>
       </c>
       <c r="B28" t="n">
-        <v>100632</v>
+        <v>105406</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3386,21 +3386,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595446</v>
+        <v>595397</v>
       </c>
       <c r="R28" t="n">
-        <v>6290169</v>
+        <v>6290188</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127736860</v>
+        <v>127736857</v>
       </c>
       <c r="B29" t="n">
-        <v>105400</v>
+        <v>100638</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3483,21 +3483,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595397</v>
+        <v>595446</v>
       </c>
       <c r="R29" t="n">
-        <v>6290188</v>
+        <v>6290169</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3569,10 +3569,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127736844</v>
+        <v>127736859</v>
       </c>
       <c r="B30" t="n">
-        <v>105400</v>
+        <v>98374</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3580,34 +3580,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221141</v>
+        <v>223591</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595448</v>
+        <v>595396</v>
       </c>
       <c r="R30" t="n">
-        <v>6290238</v>
+        <v>6290183</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3666,10 +3670,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127736859</v>
+        <v>127736844</v>
       </c>
       <c r="B31" t="n">
-        <v>98368</v>
+        <v>105406</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3677,38 +3681,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223591</v>
+        <v>221141</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595396</v>
+        <v>595448</v>
       </c>
       <c r="R31" t="n">
-        <v>6290183</v>
+        <v>6290238</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127736721</v>
+        <v>127736842</v>
       </c>
       <c r="B32" t="n">
-        <v>98428</v>
+        <v>100638</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3778,38 +3778,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>595296</v>
+        <v>595442</v>
       </c>
       <c r="R32" t="n">
-        <v>6290259</v>
+        <v>6290205</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3836,12 +3832,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3868,10 +3864,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127736842</v>
+        <v>127736721</v>
       </c>
       <c r="B33" t="n">
-        <v>100632</v>
+        <v>98434</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,34 +3875,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>595442</v>
+        <v>595296</v>
       </c>
       <c r="R33" t="n">
-        <v>6290205</v>
+        <v>6290259</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3933,12 +3933,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3965,10 +3965,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127736715</v>
+        <v>127736851</v>
       </c>
       <c r="B34" t="n">
-        <v>95530</v>
+        <v>98478</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,34 +3976,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2676</v>
+        <v>219862</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>595213</v>
+        <v>595488</v>
       </c>
       <c r="R34" t="n">
-        <v>6290222</v>
+        <v>6290180</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4030,12 +4034,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4062,10 +4066,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127736851</v>
+        <v>127736719</v>
       </c>
       <c r="B35" t="n">
-        <v>98472</v>
+        <v>98434</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4073,21 +4077,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4101,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595488</v>
+        <v>595245</v>
       </c>
       <c r="R35" t="n">
-        <v>6290180</v>
+        <v>6290215</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4131,12 +4135,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4163,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127736719</v>
+        <v>127736861</v>
       </c>
       <c r="B36" t="n">
-        <v>98428</v>
+        <v>100638</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4174,38 +4178,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595245</v>
+        <v>595396</v>
       </c>
       <c r="R36" t="n">
-        <v>6290215</v>
+        <v>6290191</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4232,12 +4232,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4267,7 +4267,7 @@
         <v>127736848</v>
       </c>
       <c r="B37" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4361,10 +4361,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127736861</v>
+        <v>127736715</v>
       </c>
       <c r="B38" t="n">
-        <v>100632</v>
+        <v>95536</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4372,21 +4372,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>2676</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>595396</v>
+        <v>595213</v>
       </c>
       <c r="R38" t="n">
-        <v>6290191</v>
+        <v>6290222</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4461,7 +4461,7 @@
         <v>127736832</v>
       </c>
       <c r="B39" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>127736724</v>
       </c>
       <c r="B40" t="n">
-        <v>98425</v>
+        <v>98431</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127736855</v>
+        <v>127736827</v>
       </c>
       <c r="B41" t="n">
-        <v>110544</v>
+        <v>100638</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4667,21 +4667,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>595472</v>
+        <v>595214</v>
       </c>
       <c r="R41" t="n">
-        <v>6290168</v>
+        <v>6290272</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4753,10 +4753,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127736725</v>
+        <v>127736836</v>
       </c>
       <c r="B42" t="n">
-        <v>98428</v>
+        <v>100638</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4764,38 +4764,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>595345</v>
+        <v>595321</v>
       </c>
       <c r="R42" t="n">
-        <v>6290259</v>
+        <v>6290251</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4822,12 +4818,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4854,10 +4850,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127736836</v>
+        <v>127736855</v>
       </c>
       <c r="B43" t="n">
-        <v>100632</v>
+        <v>110550</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4865,21 +4861,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4889,10 +4885,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>595321</v>
+        <v>595472</v>
       </c>
       <c r="R43" t="n">
-        <v>6290251</v>
+        <v>6290168</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4951,10 +4947,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127736827</v>
+        <v>127736725</v>
       </c>
       <c r="B44" t="n">
-        <v>100632</v>
+        <v>98434</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4962,34 +4958,38 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>595214</v>
+        <v>595345</v>
       </c>
       <c r="R44" t="n">
-        <v>6290272</v>
+        <v>6290259</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5016,12 +5016,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5048,10 +5048,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127736846</v>
+        <v>127736874</v>
       </c>
       <c r="B45" t="n">
-        <v>110544</v>
+        <v>100638</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5059,21 +5059,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5083,10 +5083,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>595473</v>
+        <v>595234</v>
       </c>
       <c r="R45" t="n">
-        <v>6290238</v>
+        <v>6290231</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5148,7 +5148,7 @@
         <v>127736737</v>
       </c>
       <c r="B46" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5246,10 +5246,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127736720</v>
+        <v>127736846</v>
       </c>
       <c r="B47" t="n">
-        <v>98428</v>
+        <v>110550</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5257,38 +5257,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>595305</v>
+        <v>595473</v>
       </c>
       <c r="R47" t="n">
-        <v>6290257</v>
+        <v>6290238</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5315,12 +5311,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5347,10 +5343,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127736874</v>
+        <v>127736720</v>
       </c>
       <c r="B48" t="n">
-        <v>100632</v>
+        <v>98434</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5358,34 +5354,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>595234</v>
+        <v>595305</v>
       </c>
       <c r="R48" t="n">
-        <v>6290231</v>
+        <v>6290257</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5444,10 +5444,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127736858</v>
+        <v>127736852</v>
       </c>
       <c r="B49" t="n">
-        <v>98473</v>
+        <v>105406</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5455,38 +5455,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219847</v>
+        <v>221141</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>595407</v>
+        <v>595490</v>
       </c>
       <c r="R49" t="n">
-        <v>6290191</v>
+        <v>6290176</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5545,10 +5541,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127736852</v>
+        <v>127736858</v>
       </c>
       <c r="B50" t="n">
-        <v>105400</v>
+        <v>98479</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5556,34 +5552,38 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221141</v>
+        <v>219847</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>595490</v>
+        <v>595407</v>
       </c>
       <c r="R50" t="n">
-        <v>6290176</v>
+        <v>6290191</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5645,7 +5645,7 @@
         <v>127736723</v>
       </c>
       <c r="B51" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>127736736</v>
       </c>
       <c r="B52" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>127736833</v>
       </c>
       <c r="B53" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>127736871</v>
       </c>
       <c r="B54" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127736866</v>
+        <v>127736727</v>
       </c>
       <c r="B55" t="n">
-        <v>110544</v>
+        <v>98434</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6053,34 +6053,38 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>595318</v>
+        <v>595482</v>
       </c>
       <c r="R55" t="n">
-        <v>6290207</v>
+        <v>6290215</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6107,12 +6111,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6139,10 +6143,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127736727</v>
+        <v>127736717</v>
       </c>
       <c r="B56" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6169,7 +6173,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6178,10 +6182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>595482</v>
+        <v>595312</v>
       </c>
       <c r="R56" t="n">
-        <v>6290215</v>
+        <v>6290198</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6240,10 +6244,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127736717</v>
+        <v>127736866</v>
       </c>
       <c r="B57" t="n">
-        <v>98428</v>
+        <v>110550</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6251,38 +6255,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>595312</v>
+        <v>595318</v>
       </c>
       <c r="R57" t="n">
-        <v>6290198</v>
+        <v>6290207</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6309,12 +6309,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6344,7 +6344,7 @@
         <v>127736826</v>
       </c>
       <c r="B58" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>127736726</v>
       </c>
       <c r="B59" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>127736854</v>
       </c>
       <c r="B60" t="n">
-        <v>102954</v>
+        <v>102960</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6640,10 +6640,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127736835</v>
+        <v>127736840</v>
       </c>
       <c r="B61" t="n">
-        <v>105400</v>
+        <v>105406</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>595320</v>
+        <v>595387</v>
       </c>
       <c r="R61" t="n">
-        <v>6290253</v>
+        <v>6290227</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6737,10 +6737,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127736800</v>
+        <v>127736835</v>
       </c>
       <c r="B62" t="n">
-        <v>105400</v>
+        <v>105406</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>595399</v>
+        <v>595320</v>
       </c>
       <c r="R62" t="n">
-        <v>6290260</v>
+        <v>6290253</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6834,10 +6834,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127736840</v>
+        <v>127736856</v>
       </c>
       <c r="B63" t="n">
-        <v>105400</v>
+        <v>105406</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>595387</v>
+        <v>595446</v>
       </c>
       <c r="R63" t="n">
-        <v>6290227</v>
+        <v>6290169</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6931,10 +6931,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127736856</v>
+        <v>127736800</v>
       </c>
       <c r="B64" t="n">
-        <v>105400</v>
+        <v>105406</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>595446</v>
+        <v>595399</v>
       </c>
       <c r="R64" t="n">
-        <v>6290169</v>
+        <v>6290260</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7031,7 +7031,7 @@
         <v>127736716</v>
       </c>
       <c r="B65" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>127736838</v>
       </c>
       <c r="B66" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>127736853</v>
       </c>
       <c r="B67" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>127736870</v>
       </c>
       <c r="B68" t="n">
-        <v>110544</v>
+        <v>110550</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127736718</v>
+        <v>127736865</v>
       </c>
       <c r="B69" t="n">
-        <v>98428</v>
+        <v>105406</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7431,38 +7431,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>221141</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>595293</v>
+        <v>595335</v>
       </c>
       <c r="R69" t="n">
-        <v>6290204</v>
+        <v>6290212</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7489,12 +7485,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7524,7 +7520,7 @@
         <v>127736837</v>
       </c>
       <c r="B70" t="n">
-        <v>105400</v>
+        <v>105406</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7621,7 +7617,7 @@
         <v>127736863</v>
       </c>
       <c r="B71" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7715,10 +7711,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127736865</v>
+        <v>127736718</v>
       </c>
       <c r="B72" t="n">
-        <v>105400</v>
+        <v>98434</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7726,34 +7722,38 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221141</v>
+        <v>219798</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>595335</v>
+        <v>595293</v>
       </c>
       <c r="R72" t="n">
-        <v>6290212</v>
+        <v>6290204</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7780,12 +7780,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3087,7 +3087,7 @@
         <v>127736872</v>
       </c>
       <c r="B25" t="n">
-        <v>105406</v>
+        <v>105409</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>127736831</v>
       </c>
       <c r="B26" t="n">
-        <v>105406</v>
+        <v>105409</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>127736867</v>
       </c>
       <c r="B27" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3375,10 +3375,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127736860</v>
+        <v>127736857</v>
       </c>
       <c r="B28" t="n">
-        <v>105406</v>
+        <v>100641</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3386,21 +3386,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595397</v>
+        <v>595446</v>
       </c>
       <c r="R28" t="n">
-        <v>6290188</v>
+        <v>6290169</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127736857</v>
+        <v>127736860</v>
       </c>
       <c r="B29" t="n">
-        <v>100638</v>
+        <v>105409</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3483,21 +3483,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595446</v>
+        <v>595397</v>
       </c>
       <c r="R29" t="n">
-        <v>6290169</v>
+        <v>6290188</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3569,10 +3569,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127736859</v>
+        <v>127736844</v>
       </c>
       <c r="B30" t="n">
-        <v>98374</v>
+        <v>105409</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3580,38 +3580,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>223591</v>
+        <v>221141</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595396</v>
+        <v>595448</v>
       </c>
       <c r="R30" t="n">
-        <v>6290183</v>
+        <v>6290238</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3670,10 +3666,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127736844</v>
+        <v>127736859</v>
       </c>
       <c r="B31" t="n">
-        <v>105406</v>
+        <v>98377</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3681,34 +3677,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221141</v>
+        <v>223591</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595448</v>
+        <v>595396</v>
       </c>
       <c r="R31" t="n">
-        <v>6290238</v>
+        <v>6290183</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127736842</v>
+        <v>127736721</v>
       </c>
       <c r="B32" t="n">
-        <v>100638</v>
+        <v>98437</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3778,34 +3778,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>595442</v>
+        <v>595296</v>
       </c>
       <c r="R32" t="n">
-        <v>6290205</v>
+        <v>6290259</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3832,12 +3836,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3864,10 +3868,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127736721</v>
+        <v>127736842</v>
       </c>
       <c r="B33" t="n">
-        <v>98434</v>
+        <v>100641</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3875,38 +3879,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>595296</v>
+        <v>595442</v>
       </c>
       <c r="R33" t="n">
-        <v>6290259</v>
+        <v>6290205</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3933,12 +3933,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3968,7 +3968,7 @@
         <v>127736851</v>
       </c>
       <c r="B34" t="n">
-        <v>98478</v>
+        <v>98481</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>127736719</v>
       </c>
       <c r="B35" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>127736861</v>
       </c>
       <c r="B36" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127736848</v>
+        <v>127736715</v>
       </c>
       <c r="B37" t="n">
-        <v>100638</v>
+        <v>95539</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4275,21 +4275,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>2676</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595470</v>
+        <v>595213</v>
       </c>
       <c r="R37" t="n">
-        <v>6290237</v>
+        <v>6290222</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4329,12 +4329,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4361,10 +4361,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127736715</v>
+        <v>127736848</v>
       </c>
       <c r="B38" t="n">
-        <v>95536</v>
+        <v>100641</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4372,21 +4372,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2676</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>595213</v>
+        <v>595470</v>
       </c>
       <c r="R38" t="n">
-        <v>6290222</v>
+        <v>6290237</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4458,10 +4458,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127736832</v>
+        <v>127736724</v>
       </c>
       <c r="B39" t="n">
-        <v>100638</v>
+        <v>98434</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4469,34 +4469,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>219797</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>595287</v>
+        <v>595326</v>
       </c>
       <c r="R39" t="n">
-        <v>6290259</v>
+        <v>6290257</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4523,12 +4527,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4555,10 +4559,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127736724</v>
+        <v>127736832</v>
       </c>
       <c r="B40" t="n">
-        <v>98431</v>
+        <v>100641</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4566,38 +4570,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219797</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>595326</v>
+        <v>595287</v>
       </c>
       <c r="R40" t="n">
-        <v>6290257</v>
+        <v>6290259</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4656,10 +4656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127736827</v>
+        <v>127736855</v>
       </c>
       <c r="B41" t="n">
-        <v>100638</v>
+        <v>110553</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4667,21 +4667,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>595214</v>
+        <v>595472</v>
       </c>
       <c r="R41" t="n">
-        <v>6290272</v>
+        <v>6290168</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4753,10 +4753,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127736836</v>
+        <v>127736725</v>
       </c>
       <c r="B42" t="n">
-        <v>100638</v>
+        <v>98437</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4764,34 +4764,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>595321</v>
+        <v>595345</v>
       </c>
       <c r="R42" t="n">
-        <v>6290251</v>
+        <v>6290259</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4818,12 +4822,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4850,10 +4854,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127736855</v>
+        <v>127736836</v>
       </c>
       <c r="B43" t="n">
-        <v>110550</v>
+        <v>100641</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4861,21 +4865,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4885,10 +4889,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>595472</v>
+        <v>595321</v>
       </c>
       <c r="R43" t="n">
-        <v>6290168</v>
+        <v>6290251</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4947,10 +4951,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127736725</v>
+        <v>127736827</v>
       </c>
       <c r="B44" t="n">
-        <v>98434</v>
+        <v>100641</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4958,38 +4962,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>595345</v>
+        <v>595214</v>
       </c>
       <c r="R44" t="n">
-        <v>6290259</v>
+        <v>6290272</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5016,12 +5016,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5048,10 +5048,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127736874</v>
+        <v>127736737</v>
       </c>
       <c r="B45" t="n">
-        <v>100638</v>
+        <v>98437</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5059,34 +5059,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>595234</v>
+        <v>595256</v>
       </c>
       <c r="R45" t="n">
-        <v>6290231</v>
+        <v>6290277</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5113,12 +5117,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5145,10 +5149,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127736737</v>
+        <v>127736846</v>
       </c>
       <c r="B46" t="n">
-        <v>98434</v>
+        <v>110553</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5156,38 +5160,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>595256</v>
+        <v>595473</v>
       </c>
       <c r="R46" t="n">
-        <v>6290277</v>
+        <v>6290238</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5214,12 +5214,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5246,10 +5246,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127736846</v>
+        <v>127736720</v>
       </c>
       <c r="B47" t="n">
-        <v>110550</v>
+        <v>98437</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5257,34 +5257,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>595473</v>
+        <v>595305</v>
       </c>
       <c r="R47" t="n">
-        <v>6290238</v>
+        <v>6290257</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5311,12 +5315,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5343,10 +5347,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127736720</v>
+        <v>127736874</v>
       </c>
       <c r="B48" t="n">
-        <v>98434</v>
+        <v>100641</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5354,38 +5358,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>595305</v>
+        <v>595234</v>
       </c>
       <c r="R48" t="n">
-        <v>6290257</v>
+        <v>6290231</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5447,7 +5447,7 @@
         <v>127736852</v>
       </c>
       <c r="B49" t="n">
-        <v>105406</v>
+        <v>105409</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>127736858</v>
       </c>
       <c r="B50" t="n">
-        <v>98479</v>
+        <v>98482</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>127736723</v>
       </c>
       <c r="B51" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>127736736</v>
       </c>
       <c r="B52" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>127736833</v>
       </c>
       <c r="B53" t="n">
-        <v>98478</v>
+        <v>98481</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>127736871</v>
       </c>
       <c r="B54" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>127736727</v>
       </c>
       <c r="B55" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>127736717</v>
       </c>
       <c r="B56" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>127736866</v>
       </c>
       <c r="B57" t="n">
-        <v>110550</v>
+        <v>110553</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>127736826</v>
       </c>
       <c r="B58" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>127736726</v>
       </c>
       <c r="B59" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6543,10 +6543,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127736854</v>
+        <v>127736840</v>
       </c>
       <c r="B60" t="n">
-        <v>102960</v>
+        <v>105409</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6554,16 +6554,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222002</v>
+        <v>221141</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>595486</v>
+        <v>595387</v>
       </c>
       <c r="R60" t="n">
-        <v>6290171</v>
+        <v>6290227</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6640,10 +6640,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127736840</v>
+        <v>127736835</v>
       </c>
       <c r="B61" t="n">
-        <v>105406</v>
+        <v>105409</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>595387</v>
+        <v>595320</v>
       </c>
       <c r="R61" t="n">
-        <v>6290227</v>
+        <v>6290253</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6737,10 +6737,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127736835</v>
+        <v>127736856</v>
       </c>
       <c r="B62" t="n">
-        <v>105406</v>
+        <v>105409</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>595320</v>
+        <v>595446</v>
       </c>
       <c r="R62" t="n">
-        <v>6290253</v>
+        <v>6290169</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6834,10 +6834,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127736856</v>
+        <v>127736800</v>
       </c>
       <c r="B63" t="n">
-        <v>105406</v>
+        <v>105409</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>595446</v>
+        <v>595399</v>
       </c>
       <c r="R63" t="n">
-        <v>6290169</v>
+        <v>6290260</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6931,10 +6931,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127736800</v>
+        <v>127736854</v>
       </c>
       <c r="B64" t="n">
-        <v>105406</v>
+        <v>102963</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6942,16 +6942,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221141</v>
+        <v>222002</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>595399</v>
+        <v>595486</v>
       </c>
       <c r="R64" t="n">
-        <v>6290260</v>
+        <v>6290171</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7031,7 +7031,7 @@
         <v>127736716</v>
       </c>
       <c r="B65" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>127736838</v>
       </c>
       <c r="B66" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7226,10 +7226,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127736853</v>
+        <v>127736870</v>
       </c>
       <c r="B67" t="n">
-        <v>100638</v>
+        <v>110553</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7237,21 +7237,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7261,10 +7261,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>595491</v>
+        <v>595272</v>
       </c>
       <c r="R67" t="n">
-        <v>6290172</v>
+        <v>6290205</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7323,10 +7323,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127736870</v>
+        <v>127736853</v>
       </c>
       <c r="B68" t="n">
-        <v>110550</v>
+        <v>100641</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7334,21 +7334,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7358,10 +7358,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>595272</v>
+        <v>595491</v>
       </c>
       <c r="R68" t="n">
-        <v>6290205</v>
+        <v>6290172</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7423,7 +7423,7 @@
         <v>127736865</v>
       </c>
       <c r="B69" t="n">
-        <v>105406</v>
+        <v>105409</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>127736837</v>
       </c>
       <c r="B70" t="n">
-        <v>105406</v>
+        <v>105409</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7614,10 +7614,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127736863</v>
+        <v>127736718</v>
       </c>
       <c r="B71" t="n">
-        <v>100638</v>
+        <v>98437</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7625,34 +7625,38 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>595354</v>
+        <v>595293</v>
       </c>
       <c r="R71" t="n">
-        <v>6290194</v>
+        <v>6290204</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7679,12 +7683,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7711,10 +7715,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127736718</v>
+        <v>127736863</v>
       </c>
       <c r="B72" t="n">
-        <v>98434</v>
+        <v>100641</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7722,38 +7726,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>595293</v>
+        <v>595354</v>
       </c>
       <c r="R72" t="n">
-        <v>6290204</v>
+        <v>6290194</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7780,12 +7780,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3087,7 +3087,7 @@
         <v>127736872</v>
       </c>
       <c r="B25" t="n">
-        <v>105409</v>
+        <v>105417</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>127736831</v>
       </c>
       <c r="B26" t="n">
-        <v>105409</v>
+        <v>105417</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>127736867</v>
       </c>
       <c r="B27" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3375,10 +3375,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127736857</v>
+        <v>127736860</v>
       </c>
       <c r="B28" t="n">
-        <v>100641</v>
+        <v>105417</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3386,21 +3386,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595446</v>
+        <v>595397</v>
       </c>
       <c r="R28" t="n">
-        <v>6290169</v>
+        <v>6290188</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127736860</v>
+        <v>127736857</v>
       </c>
       <c r="B29" t="n">
-        <v>105409</v>
+        <v>100649</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3483,21 +3483,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595397</v>
+        <v>595446</v>
       </c>
       <c r="R29" t="n">
-        <v>6290188</v>
+        <v>6290169</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3572,7 +3572,7 @@
         <v>127736844</v>
       </c>
       <c r="B30" t="n">
-        <v>105409</v>
+        <v>105417</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>127736859</v>
       </c>
       <c r="B31" t="n">
-        <v>98377</v>
+        <v>98385</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>127736721</v>
       </c>
       <c r="B32" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>127736842</v>
       </c>
       <c r="B33" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127736851</v>
+        <v>127736848</v>
       </c>
       <c r="B34" t="n">
-        <v>98481</v>
+        <v>100649</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,38 +3976,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>595488</v>
+        <v>595470</v>
       </c>
       <c r="R34" t="n">
-        <v>6290180</v>
+        <v>6290237</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,10 +4062,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127736719</v>
+        <v>127736861</v>
       </c>
       <c r="B35" t="n">
-        <v>98437</v>
+        <v>100649</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4077,38 +4073,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595245</v>
+        <v>595396</v>
       </c>
       <c r="R35" t="n">
-        <v>6290215</v>
+        <v>6290191</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4135,12 +4127,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4167,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127736861</v>
+        <v>127736851</v>
       </c>
       <c r="B36" t="n">
-        <v>100641</v>
+        <v>98489</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4178,34 +4170,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595396</v>
+        <v>595488</v>
       </c>
       <c r="R36" t="n">
-        <v>6290191</v>
+        <v>6290180</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4264,10 +4260,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127736715</v>
+        <v>127736719</v>
       </c>
       <c r="B37" t="n">
-        <v>95539</v>
+        <v>98445</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4275,34 +4271,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2676</v>
+        <v>219798</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595213</v>
+        <v>595245</v>
       </c>
       <c r="R37" t="n">
-        <v>6290222</v>
+        <v>6290215</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4361,10 +4361,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127736848</v>
+        <v>127736715</v>
       </c>
       <c r="B38" t="n">
-        <v>100641</v>
+        <v>95547</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4372,21 +4372,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>2676</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>595470</v>
+        <v>595213</v>
       </c>
       <c r="R38" t="n">
-        <v>6290237</v>
+        <v>6290222</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4461,7 +4461,7 @@
         <v>127736724</v>
       </c>
       <c r="B39" t="n">
-        <v>98434</v>
+        <v>98442</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>127736832</v>
       </c>
       <c r="B40" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>127736855</v>
       </c>
       <c r="B41" t="n">
-        <v>110553</v>
+        <v>110561</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>127736725</v>
       </c>
       <c r="B42" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>127736836</v>
       </c>
       <c r="B43" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>127736827</v>
       </c>
       <c r="B44" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>127736737</v>
       </c>
       <c r="B45" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127736846</v>
+        <v>127736720</v>
       </c>
       <c r="B46" t="n">
-        <v>110553</v>
+        <v>98445</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5160,34 +5160,38 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>595473</v>
+        <v>595305</v>
       </c>
       <c r="R46" t="n">
-        <v>6290238</v>
+        <v>6290257</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5214,12 +5218,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5246,10 +5250,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127736720</v>
+        <v>127736874</v>
       </c>
       <c r="B47" t="n">
-        <v>98437</v>
+        <v>100649</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5257,38 +5261,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>595305</v>
+        <v>595234</v>
       </c>
       <c r="R47" t="n">
-        <v>6290257</v>
+        <v>6290231</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5347,10 +5347,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127736874</v>
+        <v>127736846</v>
       </c>
       <c r="B48" t="n">
-        <v>100641</v>
+        <v>110561</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5358,21 +5358,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>595234</v>
+        <v>595473</v>
       </c>
       <c r="R48" t="n">
-        <v>6290231</v>
+        <v>6290238</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5444,10 +5444,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127736852</v>
+        <v>127736858</v>
       </c>
       <c r="B49" t="n">
-        <v>105409</v>
+        <v>98490</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5455,34 +5455,38 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221141</v>
+        <v>219847</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>595490</v>
+        <v>595407</v>
       </c>
       <c r="R49" t="n">
-        <v>6290176</v>
+        <v>6290191</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5541,10 +5545,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127736858</v>
+        <v>127736852</v>
       </c>
       <c r="B50" t="n">
-        <v>98482</v>
+        <v>105417</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5552,38 +5556,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219847</v>
+        <v>221141</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>595407</v>
+        <v>595490</v>
       </c>
       <c r="R50" t="n">
-        <v>6290191</v>
+        <v>6290176</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5645,7 +5645,7 @@
         <v>127736723</v>
       </c>
       <c r="B51" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>127736736</v>
       </c>
       <c r="B52" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>127736833</v>
       </c>
       <c r="B53" t="n">
-        <v>98481</v>
+        <v>98489</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5945,10 +5945,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127736871</v>
+        <v>127736866</v>
       </c>
       <c r="B54" t="n">
-        <v>100641</v>
+        <v>110561</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5956,21 +5956,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5980,10 +5980,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>595263</v>
+        <v>595318</v>
       </c>
       <c r="R54" t="n">
-        <v>6290211</v>
+        <v>6290207</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6042,10 +6042,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127736727</v>
+        <v>127736871</v>
       </c>
       <c r="B55" t="n">
-        <v>98437</v>
+        <v>100649</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6053,38 +6053,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>595482</v>
+        <v>595263</v>
       </c>
       <c r="R55" t="n">
-        <v>6290215</v>
+        <v>6290211</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6111,12 +6107,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6143,10 +6139,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127736717</v>
+        <v>127736727</v>
       </c>
       <c r="B56" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6173,7 +6169,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6182,10 +6178,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>595312</v>
+        <v>595482</v>
       </c>
       <c r="R56" t="n">
-        <v>6290198</v>
+        <v>6290215</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6244,10 +6240,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127736866</v>
+        <v>127736717</v>
       </c>
       <c r="B57" t="n">
-        <v>110553</v>
+        <v>98445</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6255,34 +6251,38 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>595318</v>
+        <v>595312</v>
       </c>
       <c r="R57" t="n">
-        <v>6290207</v>
+        <v>6290198</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6309,12 +6309,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6344,7 +6344,7 @@
         <v>127736826</v>
       </c>
       <c r="B58" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>127736726</v>
       </c>
       <c r="B59" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6543,10 +6543,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127736840</v>
+        <v>127736854</v>
       </c>
       <c r="B60" t="n">
-        <v>105409</v>
+        <v>102971</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6554,16 +6554,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221141</v>
+        <v>222002</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>595387</v>
+        <v>595486</v>
       </c>
       <c r="R60" t="n">
-        <v>6290227</v>
+        <v>6290171</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6640,10 +6640,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127736835</v>
+        <v>127736840</v>
       </c>
       <c r="B61" t="n">
-        <v>105409</v>
+        <v>105417</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>595320</v>
+        <v>595387</v>
       </c>
       <c r="R61" t="n">
-        <v>6290253</v>
+        <v>6290227</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6737,10 +6737,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127736856</v>
+        <v>127736835</v>
       </c>
       <c r="B62" t="n">
-        <v>105409</v>
+        <v>105417</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>595446</v>
+        <v>595320</v>
       </c>
       <c r="R62" t="n">
-        <v>6290169</v>
+        <v>6290253</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6834,10 +6834,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127736800</v>
+        <v>127736856</v>
       </c>
       <c r="B63" t="n">
-        <v>105409</v>
+        <v>105417</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>595399</v>
+        <v>595446</v>
       </c>
       <c r="R63" t="n">
-        <v>6290260</v>
+        <v>6290169</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6931,10 +6931,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127736854</v>
+        <v>127736800</v>
       </c>
       <c r="B64" t="n">
-        <v>102963</v>
+        <v>105417</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6942,16 +6942,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222002</v>
+        <v>221141</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>595486</v>
+        <v>595399</v>
       </c>
       <c r="R64" t="n">
-        <v>6290171</v>
+        <v>6290260</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7028,10 +7028,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127736716</v>
+        <v>127736838</v>
       </c>
       <c r="B65" t="n">
-        <v>98437</v>
+        <v>100649</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7039,38 +7039,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>595320</v>
+        <v>595371</v>
       </c>
       <c r="R65" t="n">
-        <v>6290193</v>
+        <v>6290254</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7097,12 +7093,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7129,10 +7125,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127736838</v>
+        <v>127736716</v>
       </c>
       <c r="B66" t="n">
-        <v>100641</v>
+        <v>98445</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7140,34 +7136,38 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>595371</v>
+        <v>595320</v>
       </c>
       <c r="R66" t="n">
-        <v>6290254</v>
+        <v>6290193</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7194,12 +7194,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7229,7 +7229,7 @@
         <v>127736870</v>
       </c>
       <c r="B67" t="n">
-        <v>110553</v>
+        <v>110561</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>127736853</v>
       </c>
       <c r="B68" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>127736865</v>
       </c>
       <c r="B69" t="n">
-        <v>105409</v>
+        <v>105417</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>127736837</v>
       </c>
       <c r="B70" t="n">
-        <v>105409</v>
+        <v>105417</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7614,10 +7614,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127736718</v>
+        <v>127736863</v>
       </c>
       <c r="B71" t="n">
-        <v>98437</v>
+        <v>100649</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7625,38 +7625,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>595293</v>
+        <v>595354</v>
       </c>
       <c r="R71" t="n">
-        <v>6290204</v>
+        <v>6290194</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7683,12 +7679,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7715,10 +7711,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127736863</v>
+        <v>127736718</v>
       </c>
       <c r="B72" t="n">
-        <v>100641</v>
+        <v>98445</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7726,34 +7722,38 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>595354</v>
+        <v>595293</v>
       </c>
       <c r="R72" t="n">
-        <v>6290194</v>
+        <v>6290204</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7780,12 +7780,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3084,10 +3084,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127736872</v>
+        <v>127736867</v>
       </c>
       <c r="B25" t="n">
-        <v>105417</v>
+        <v>100650</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3095,21 +3095,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595265</v>
+        <v>595320</v>
       </c>
       <c r="R25" t="n">
-        <v>6290208</v>
+        <v>6290206</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,10 +3181,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127736831</v>
+        <v>127736872</v>
       </c>
       <c r="B26" t="n">
-        <v>105417</v>
+        <v>105418</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595286</v>
+        <v>595265</v>
       </c>
       <c r="R26" t="n">
-        <v>6290259</v>
+        <v>6290208</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3278,10 +3278,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127736867</v>
+        <v>127736831</v>
       </c>
       <c r="B27" t="n">
-        <v>100649</v>
+        <v>105418</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3289,21 +3289,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595320</v>
+        <v>595286</v>
       </c>
       <c r="R27" t="n">
-        <v>6290206</v>
+        <v>6290259</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,10 +3375,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127736860</v>
+        <v>127736857</v>
       </c>
       <c r="B28" t="n">
-        <v>105417</v>
+        <v>100650</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3386,21 +3386,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595397</v>
+        <v>595446</v>
       </c>
       <c r="R28" t="n">
-        <v>6290188</v>
+        <v>6290169</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127736857</v>
+        <v>127736860</v>
       </c>
       <c r="B29" t="n">
-        <v>100649</v>
+        <v>105418</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3483,21 +3483,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595446</v>
+        <v>595397</v>
       </c>
       <c r="R29" t="n">
-        <v>6290169</v>
+        <v>6290188</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3572,7 +3572,7 @@
         <v>127736844</v>
       </c>
       <c r="B30" t="n">
-        <v>105417</v>
+        <v>105418</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>127736859</v>
       </c>
       <c r="B31" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>127736721</v>
       </c>
       <c r="B32" t="n">
-        <v>98445</v>
+        <v>98446</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>127736842</v>
       </c>
       <c r="B33" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127736848</v>
+        <v>127736715</v>
       </c>
       <c r="B34" t="n">
-        <v>100649</v>
+        <v>95548</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,21 +3976,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>2676</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>595470</v>
+        <v>595213</v>
       </c>
       <c r="R34" t="n">
-        <v>6290237</v>
+        <v>6290222</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4062,10 +4062,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127736861</v>
+        <v>127736851</v>
       </c>
       <c r="B35" t="n">
-        <v>100649</v>
+        <v>98490</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4073,34 +4073,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595396</v>
+        <v>595488</v>
       </c>
       <c r="R35" t="n">
-        <v>6290191</v>
+        <v>6290180</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4159,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127736851</v>
+        <v>127736719</v>
       </c>
       <c r="B36" t="n">
-        <v>98489</v>
+        <v>98446</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4170,21 +4174,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4198,10 +4202,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595488</v>
+        <v>595245</v>
       </c>
       <c r="R36" t="n">
-        <v>6290180</v>
+        <v>6290215</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4228,12 +4232,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4260,10 +4264,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127736719</v>
+        <v>127736848</v>
       </c>
       <c r="B37" t="n">
-        <v>98445</v>
+        <v>100650</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4271,38 +4275,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595245</v>
+        <v>595470</v>
       </c>
       <c r="R37" t="n">
-        <v>6290215</v>
+        <v>6290237</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4329,12 +4329,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4361,10 +4361,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127736715</v>
+        <v>127736861</v>
       </c>
       <c r="B38" t="n">
-        <v>95547</v>
+        <v>100650</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4372,21 +4372,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2676</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>595213</v>
+        <v>595396</v>
       </c>
       <c r="R38" t="n">
-        <v>6290222</v>
+        <v>6290191</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4461,7 +4461,7 @@
         <v>127736724</v>
       </c>
       <c r="B39" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>127736832</v>
       </c>
       <c r="B40" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127736855</v>
+        <v>127736725</v>
       </c>
       <c r="B41" t="n">
-        <v>110561</v>
+        <v>98446</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4667,34 +4667,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>595472</v>
+        <v>595345</v>
       </c>
       <c r="R41" t="n">
-        <v>6290168</v>
+        <v>6290259</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4721,12 +4725,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4753,10 +4757,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127736725</v>
+        <v>127736836</v>
       </c>
       <c r="B42" t="n">
-        <v>98445</v>
+        <v>100650</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4764,38 +4768,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>595345</v>
+        <v>595321</v>
       </c>
       <c r="R42" t="n">
-        <v>6290259</v>
+        <v>6290251</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4854,10 +4854,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127736836</v>
+        <v>127736827</v>
       </c>
       <c r="B43" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4889,10 +4889,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>595321</v>
+        <v>595214</v>
       </c>
       <c r="R43" t="n">
-        <v>6290251</v>
+        <v>6290272</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4951,10 +4951,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127736827</v>
+        <v>127736855</v>
       </c>
       <c r="B44" t="n">
-        <v>100649</v>
+        <v>110562</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4962,21 +4962,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>595214</v>
+        <v>595472</v>
       </c>
       <c r="R44" t="n">
-        <v>6290272</v>
+        <v>6290168</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5051,7 +5051,7 @@
         <v>127736737</v>
       </c>
       <c r="B45" t="n">
-        <v>98445</v>
+        <v>98446</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>127736720</v>
       </c>
       <c r="B46" t="n">
-        <v>98445</v>
+        <v>98446</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5250,10 +5250,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127736874</v>
+        <v>127736846</v>
       </c>
       <c r="B47" t="n">
-        <v>100649</v>
+        <v>110562</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5261,21 +5261,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5285,10 +5285,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>595234</v>
+        <v>595473</v>
       </c>
       <c r="R47" t="n">
-        <v>6290231</v>
+        <v>6290238</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5347,10 +5347,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127736846</v>
+        <v>127736874</v>
       </c>
       <c r="B48" t="n">
-        <v>110561</v>
+        <v>100650</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5358,21 +5358,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>595473</v>
+        <v>595234</v>
       </c>
       <c r="R48" t="n">
-        <v>6290238</v>
+        <v>6290231</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5447,7 +5447,7 @@
         <v>127736858</v>
       </c>
       <c r="B49" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>127736852</v>
       </c>
       <c r="B50" t="n">
-        <v>105417</v>
+        <v>105418</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>127736723</v>
       </c>
       <c r="B51" t="n">
-        <v>98445</v>
+        <v>98446</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>127736736</v>
       </c>
       <c r="B52" t="n">
-        <v>98445</v>
+        <v>98446</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>127736833</v>
       </c>
       <c r="B53" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5945,10 +5945,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127736866</v>
+        <v>127736727</v>
       </c>
       <c r="B54" t="n">
-        <v>110561</v>
+        <v>98446</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5956,34 +5956,38 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>595318</v>
+        <v>595482</v>
       </c>
       <c r="R54" t="n">
-        <v>6290207</v>
+        <v>6290215</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6010,12 +6014,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6042,10 +6046,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127736871</v>
+        <v>127736717</v>
       </c>
       <c r="B55" t="n">
-        <v>100649</v>
+        <v>98446</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6053,34 +6057,38 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>595263</v>
+        <v>595312</v>
       </c>
       <c r="R55" t="n">
-        <v>6290211</v>
+        <v>6290198</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6107,12 +6115,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6139,10 +6147,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127736727</v>
+        <v>127736826</v>
       </c>
       <c r="B56" t="n">
-        <v>98445</v>
+        <v>98385</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6150,26 +6158,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219798</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6178,10 +6186,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>595482</v>
+        <v>595215</v>
       </c>
       <c r="R56" t="n">
-        <v>6290215</v>
+        <v>6290279</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6208,12 +6216,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6240,10 +6248,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127736717</v>
+        <v>127736726</v>
       </c>
       <c r="B57" t="n">
-        <v>98445</v>
+        <v>98446</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6270,7 +6278,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6279,10 +6287,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>595312</v>
+        <v>595419</v>
       </c>
       <c r="R57" t="n">
-        <v>6290198</v>
+        <v>6290207</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6341,10 +6349,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127736826</v>
+        <v>127736871</v>
       </c>
       <c r="B58" t="n">
-        <v>98384</v>
+        <v>100650</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6352,38 +6360,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219790</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>595215</v>
+        <v>595263</v>
       </c>
       <c r="R58" t="n">
-        <v>6290279</v>
+        <v>6290211</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6442,10 +6446,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127736726</v>
+        <v>127736866</v>
       </c>
       <c r="B59" t="n">
-        <v>98445</v>
+        <v>110562</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6453,35 +6457,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>595419</v>
+        <v>595318</v>
       </c>
       <c r="R59" t="n">
         <v>6290207</v>
@@ -6511,12 +6511,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6546,7 +6546,7 @@
         <v>127736854</v>
       </c>
       <c r="B60" t="n">
-        <v>102971</v>
+        <v>102972</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>127736840</v>
       </c>
       <c r="B61" t="n">
-        <v>105417</v>
+        <v>105418</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>127736835</v>
       </c>
       <c r="B62" t="n">
-        <v>105417</v>
+        <v>105418</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6834,10 +6834,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127736856</v>
+        <v>127736800</v>
       </c>
       <c r="B63" t="n">
-        <v>105417</v>
+        <v>105418</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>595446</v>
+        <v>595399</v>
       </c>
       <c r="R63" t="n">
-        <v>6290169</v>
+        <v>6290260</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6931,10 +6931,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127736800</v>
+        <v>127736856</v>
       </c>
       <c r="B64" t="n">
-        <v>105417</v>
+        <v>105418</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>595399</v>
+        <v>595446</v>
       </c>
       <c r="R64" t="n">
-        <v>6290260</v>
+        <v>6290169</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7028,10 +7028,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127736838</v>
+        <v>127736716</v>
       </c>
       <c r="B65" t="n">
-        <v>100649</v>
+        <v>98446</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7039,34 +7039,38 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>595371</v>
+        <v>595320</v>
       </c>
       <c r="R65" t="n">
-        <v>6290254</v>
+        <v>6290193</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7093,12 +7097,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7125,10 +7129,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127736716</v>
+        <v>127736838</v>
       </c>
       <c r="B66" t="n">
-        <v>98445</v>
+        <v>100650</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7136,38 +7140,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>595320</v>
+        <v>595371</v>
       </c>
       <c r="R66" t="n">
-        <v>6290193</v>
+        <v>6290254</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7194,12 +7194,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7226,10 +7226,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127736870</v>
+        <v>127736853</v>
       </c>
       <c r="B67" t="n">
-        <v>110561</v>
+        <v>100650</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7237,21 +7237,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7261,10 +7261,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>595272</v>
+        <v>595491</v>
       </c>
       <c r="R67" t="n">
-        <v>6290205</v>
+        <v>6290172</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7323,10 +7323,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127736853</v>
+        <v>127736870</v>
       </c>
       <c r="B68" t="n">
-        <v>100649</v>
+        <v>110562</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7334,21 +7334,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7358,10 +7358,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>595491</v>
+        <v>595272</v>
       </c>
       <c r="R68" t="n">
-        <v>6290172</v>
+        <v>6290205</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127736865</v>
+        <v>127736863</v>
       </c>
       <c r="B69" t="n">
-        <v>105417</v>
+        <v>100650</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7431,21 +7431,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7455,10 +7455,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>595335</v>
+        <v>595354</v>
       </c>
       <c r="R69" t="n">
-        <v>6290212</v>
+        <v>6290194</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7520,7 +7520,7 @@
         <v>127736837</v>
       </c>
       <c r="B70" t="n">
-        <v>105417</v>
+        <v>105418</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7614,10 +7614,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127736863</v>
+        <v>127736718</v>
       </c>
       <c r="B71" t="n">
-        <v>100649</v>
+        <v>98446</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7625,34 +7625,38 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>595354</v>
+        <v>595293</v>
       </c>
       <c r="R71" t="n">
-        <v>6290194</v>
+        <v>6290204</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7679,12 +7683,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7711,10 +7715,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127736718</v>
+        <v>127736865</v>
       </c>
       <c r="B72" t="n">
-        <v>98445</v>
+        <v>105418</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7722,38 +7726,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219798</v>
+        <v>221141</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>595293</v>
+        <v>595335</v>
       </c>
       <c r="R72" t="n">
-        <v>6290204</v>
+        <v>6290212</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7780,12 +7780,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3084,10 +3084,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127736867</v>
+        <v>127736872</v>
       </c>
       <c r="B25" t="n">
-        <v>100650</v>
+        <v>105418</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3095,21 +3095,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595320</v>
+        <v>595265</v>
       </c>
       <c r="R25" t="n">
-        <v>6290206</v>
+        <v>6290208</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,7 +3181,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127736872</v>
+        <v>127736831</v>
       </c>
       <c r="B26" t="n">
         <v>105418</v>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595265</v>
+        <v>595286</v>
       </c>
       <c r="R26" t="n">
-        <v>6290208</v>
+        <v>6290259</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3278,10 +3278,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127736831</v>
+        <v>127736867</v>
       </c>
       <c r="B27" t="n">
-        <v>105418</v>
+        <v>100650</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3289,21 +3289,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595286</v>
+        <v>595320</v>
       </c>
       <c r="R27" t="n">
-        <v>6290259</v>
+        <v>6290206</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3569,10 +3569,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127736844</v>
+        <v>127736859</v>
       </c>
       <c r="B30" t="n">
-        <v>105418</v>
+        <v>98386</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3580,34 +3580,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221141</v>
+        <v>223591</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595448</v>
+        <v>595396</v>
       </c>
       <c r="R30" t="n">
-        <v>6290238</v>
+        <v>6290183</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3666,10 +3670,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127736859</v>
+        <v>127736844</v>
       </c>
       <c r="B31" t="n">
-        <v>98386</v>
+        <v>105418</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3677,38 +3681,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223591</v>
+        <v>221141</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595396</v>
+        <v>595448</v>
       </c>
       <c r="R31" t="n">
-        <v>6290183</v>
+        <v>6290238</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4656,10 +4656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127736725</v>
+        <v>127736855</v>
       </c>
       <c r="B41" t="n">
-        <v>98446</v>
+        <v>110562</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4667,38 +4667,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>595345</v>
+        <v>595472</v>
       </c>
       <c r="R41" t="n">
-        <v>6290259</v>
+        <v>6290168</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4725,12 +4721,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4757,10 +4753,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127736836</v>
+        <v>127736725</v>
       </c>
       <c r="B42" t="n">
-        <v>100650</v>
+        <v>98446</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4768,34 +4764,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>595321</v>
+        <v>595345</v>
       </c>
       <c r="R42" t="n">
-        <v>6290251</v>
+        <v>6290259</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4854,7 +4854,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127736827</v>
+        <v>127736836</v>
       </c>
       <c r="B43" t="n">
         <v>100650</v>
@@ -4889,10 +4889,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>595214</v>
+        <v>595321</v>
       </c>
       <c r="R43" t="n">
-        <v>6290272</v>
+        <v>6290251</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4951,10 +4951,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127736855</v>
+        <v>127736827</v>
       </c>
       <c r="B44" t="n">
-        <v>110562</v>
+        <v>100650</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4962,21 +4962,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>595472</v>
+        <v>595214</v>
       </c>
       <c r="R44" t="n">
-        <v>6290168</v>
+        <v>6290272</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5048,10 +5048,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127736737</v>
+        <v>127736874</v>
       </c>
       <c r="B45" t="n">
-        <v>98446</v>
+        <v>100650</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5059,38 +5059,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>595256</v>
+        <v>595234</v>
       </c>
       <c r="R45" t="n">
-        <v>6290277</v>
+        <v>6290231</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5117,12 +5113,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5149,7 +5145,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127736720</v>
+        <v>127736737</v>
       </c>
       <c r="B46" t="n">
         <v>98446</v>
@@ -5179,7 +5175,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5188,10 +5184,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>595305</v>
+        <v>595256</v>
       </c>
       <c r="R46" t="n">
-        <v>6290257</v>
+        <v>6290277</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5347,10 +5343,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127736874</v>
+        <v>127736720</v>
       </c>
       <c r="B48" t="n">
-        <v>100650</v>
+        <v>98446</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5358,34 +5354,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>595234</v>
+        <v>595305</v>
       </c>
       <c r="R48" t="n">
-        <v>6290231</v>
+        <v>6290257</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5444,10 +5444,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127736858</v>
+        <v>127736852</v>
       </c>
       <c r="B49" t="n">
-        <v>98491</v>
+        <v>105418</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5455,38 +5455,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219847</v>
+        <v>221141</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>595407</v>
+        <v>595490</v>
       </c>
       <c r="R49" t="n">
-        <v>6290191</v>
+        <v>6290176</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5545,10 +5541,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127736852</v>
+        <v>127736858</v>
       </c>
       <c r="B50" t="n">
-        <v>105418</v>
+        <v>98491</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5556,34 +5552,38 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221141</v>
+        <v>219847</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>595490</v>
+        <v>595407</v>
       </c>
       <c r="R50" t="n">
-        <v>6290176</v>
+        <v>6290191</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6147,10 +6147,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127736826</v>
+        <v>127736866</v>
       </c>
       <c r="B56" t="n">
-        <v>98385</v>
+        <v>110562</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6158,38 +6158,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>219711</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>595215</v>
+        <v>595318</v>
       </c>
       <c r="R56" t="n">
-        <v>6290279</v>
+        <v>6290207</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6248,10 +6244,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127736726</v>
+        <v>127736826</v>
       </c>
       <c r="B57" t="n">
-        <v>98446</v>
+        <v>98385</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6259,26 +6255,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219798</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6287,10 +6283,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>595419</v>
+        <v>595215</v>
       </c>
       <c r="R57" t="n">
-        <v>6290207</v>
+        <v>6290279</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6317,12 +6313,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6349,10 +6345,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127736871</v>
+        <v>127736726</v>
       </c>
       <c r="B58" t="n">
-        <v>100650</v>
+        <v>98446</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6360,34 +6356,38 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>595263</v>
+        <v>595419</v>
       </c>
       <c r="R58" t="n">
-        <v>6290211</v>
+        <v>6290207</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6446,10 +6446,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127736866</v>
+        <v>127736871</v>
       </c>
       <c r="B59" t="n">
-        <v>110562</v>
+        <v>100650</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6457,21 +6457,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6481,10 +6481,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>595318</v>
+        <v>595263</v>
       </c>
       <c r="R59" t="n">
-        <v>6290207</v>
+        <v>6290211</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6543,10 +6543,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127736854</v>
+        <v>127736840</v>
       </c>
       <c r="B60" t="n">
-        <v>102972</v>
+        <v>105418</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6554,16 +6554,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222002</v>
+        <v>221141</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>595486</v>
+        <v>595387</v>
       </c>
       <c r="R60" t="n">
-        <v>6290171</v>
+        <v>6290227</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6640,7 +6640,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127736840</v>
+        <v>127736856</v>
       </c>
       <c r="B61" t="n">
         <v>105418</v>
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>595387</v>
+        <v>595446</v>
       </c>
       <c r="R61" t="n">
-        <v>6290227</v>
+        <v>6290169</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6737,7 +6737,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127736835</v>
+        <v>127736800</v>
       </c>
       <c r="B62" t="n">
         <v>105418</v>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>595320</v>
+        <v>595399</v>
       </c>
       <c r="R62" t="n">
-        <v>6290253</v>
+        <v>6290260</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6834,10 +6834,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127736800</v>
+        <v>127736854</v>
       </c>
       <c r="B63" t="n">
-        <v>105418</v>
+        <v>102972</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6845,16 +6845,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221141</v>
+        <v>222002</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>595399</v>
+        <v>595486</v>
       </c>
       <c r="R63" t="n">
-        <v>6290260</v>
+        <v>6290171</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6931,7 +6931,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127736856</v>
+        <v>127736835</v>
       </c>
       <c r="B64" t="n">
         <v>105418</v>
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>595446</v>
+        <v>595320</v>
       </c>
       <c r="R64" t="n">
-        <v>6290169</v>
+        <v>6290253</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7226,10 +7226,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127736853</v>
+        <v>127736870</v>
       </c>
       <c r="B67" t="n">
-        <v>100650</v>
+        <v>110562</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7237,21 +7237,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7261,10 +7261,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>595491</v>
+        <v>595272</v>
       </c>
       <c r="R67" t="n">
-        <v>6290172</v>
+        <v>6290205</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7323,10 +7323,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127736870</v>
+        <v>127736853</v>
       </c>
       <c r="B68" t="n">
-        <v>110562</v>
+        <v>100650</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7334,21 +7334,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7358,10 +7358,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>595272</v>
+        <v>595491</v>
       </c>
       <c r="R68" t="n">
-        <v>6290205</v>
+        <v>6290172</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127736863</v>
+        <v>127736718</v>
       </c>
       <c r="B69" t="n">
-        <v>100650</v>
+        <v>98446</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7431,34 +7431,38 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>595354</v>
+        <v>595293</v>
       </c>
       <c r="R69" t="n">
-        <v>6290194</v>
+        <v>6290204</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7485,12 +7489,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7517,7 +7521,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127736837</v>
+        <v>127736865</v>
       </c>
       <c r="B70" t="n">
         <v>105418</v>
@@ -7552,10 +7556,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>595371</v>
+        <v>595335</v>
       </c>
       <c r="R70" t="n">
-        <v>6290254</v>
+        <v>6290212</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7614,10 +7618,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127736718</v>
+        <v>127736837</v>
       </c>
       <c r="B71" t="n">
-        <v>98446</v>
+        <v>105418</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7625,38 +7629,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219798</v>
+        <v>221141</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>595293</v>
+        <v>595371</v>
       </c>
       <c r="R71" t="n">
-        <v>6290204</v>
+        <v>6290254</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7683,12 +7683,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7715,10 +7715,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127736865</v>
+        <v>127736863</v>
       </c>
       <c r="B72" t="n">
-        <v>105418</v>
+        <v>100650</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7726,21 +7726,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7750,10 +7750,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>595335</v>
+        <v>595354</v>
       </c>
       <c r="R72" t="n">
-        <v>6290212</v>
+        <v>6290194</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3087,7 +3087,7 @@
         <v>127736872</v>
       </c>
       <c r="B25" t="n">
-        <v>105418</v>
+        <v>105419</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>127736831</v>
       </c>
       <c r="B26" t="n">
-        <v>105418</v>
+        <v>105419</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>127736867</v>
       </c>
       <c r="B27" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>127736857</v>
       </c>
       <c r="B28" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>127736860</v>
       </c>
       <c r="B29" t="n">
-        <v>105418</v>
+        <v>105419</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3569,10 +3569,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127736859</v>
+        <v>127736844</v>
       </c>
       <c r="B30" t="n">
-        <v>98386</v>
+        <v>105419</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3580,38 +3580,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>223591</v>
+        <v>221141</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595396</v>
+        <v>595448</v>
       </c>
       <c r="R30" t="n">
-        <v>6290183</v>
+        <v>6290238</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3670,10 +3666,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127736844</v>
+        <v>127736859</v>
       </c>
       <c r="B31" t="n">
-        <v>105418</v>
+        <v>98387</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3681,34 +3677,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221141</v>
+        <v>223591</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595448</v>
+        <v>595396</v>
       </c>
       <c r="R31" t="n">
-        <v>6290238</v>
+        <v>6290183</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3770,7 +3770,7 @@
         <v>127736721</v>
       </c>
       <c r="B32" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>127736842</v>
       </c>
       <c r="B33" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>127736715</v>
       </c>
       <c r="B34" t="n">
-        <v>95548</v>
+        <v>95549</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>127736851</v>
       </c>
       <c r="B35" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>127736719</v>
       </c>
       <c r="B36" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>127736848</v>
       </c>
       <c r="B37" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>127736861</v>
       </c>
       <c r="B38" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4458,10 +4458,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127736724</v>
+        <v>127736832</v>
       </c>
       <c r="B39" t="n">
-        <v>98443</v>
+        <v>100651</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4469,38 +4469,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219797</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>595326</v>
+        <v>595287</v>
       </c>
       <c r="R39" t="n">
-        <v>6290257</v>
+        <v>6290259</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4527,12 +4523,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4559,10 +4555,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127736832</v>
+        <v>127736724</v>
       </c>
       <c r="B40" t="n">
-        <v>100650</v>
+        <v>98444</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4570,34 +4566,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>219797</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>595287</v>
+        <v>595326</v>
       </c>
       <c r="R40" t="n">
-        <v>6290259</v>
+        <v>6290257</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4656,10 +4656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127736855</v>
+        <v>127736725</v>
       </c>
       <c r="B41" t="n">
-        <v>110562</v>
+        <v>98447</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4667,34 +4667,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>595472</v>
+        <v>595345</v>
       </c>
       <c r="R41" t="n">
-        <v>6290168</v>
+        <v>6290259</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4721,12 +4725,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4753,10 +4757,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127736725</v>
+        <v>127736855</v>
       </c>
       <c r="B42" t="n">
-        <v>98446</v>
+        <v>110563</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4764,38 +4768,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>595345</v>
+        <v>595472</v>
       </c>
       <c r="R42" t="n">
-        <v>6290259</v>
+        <v>6290168</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4857,7 +4857,7 @@
         <v>127736836</v>
       </c>
       <c r="B43" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>127736827</v>
       </c>
       <c r="B44" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5048,10 +5048,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127736874</v>
+        <v>127736737</v>
       </c>
       <c r="B45" t="n">
-        <v>100650</v>
+        <v>98447</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5059,34 +5059,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>595234</v>
+        <v>595256</v>
       </c>
       <c r="R45" t="n">
-        <v>6290231</v>
+        <v>6290277</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5113,12 +5117,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5145,10 +5149,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127736737</v>
+        <v>127736720</v>
       </c>
       <c r="B46" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5175,7 +5179,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5184,10 +5188,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>595256</v>
+        <v>595305</v>
       </c>
       <c r="R46" t="n">
-        <v>6290277</v>
+        <v>6290257</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5249,7 +5253,7 @@
         <v>127736846</v>
       </c>
       <c r="B47" t="n">
-        <v>110562</v>
+        <v>110563</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5343,10 +5347,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127736720</v>
+        <v>127736874</v>
       </c>
       <c r="B48" t="n">
-        <v>98446</v>
+        <v>100651</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5354,38 +5358,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>595305</v>
+        <v>595234</v>
       </c>
       <c r="R48" t="n">
-        <v>6290257</v>
+        <v>6290231</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5444,10 +5444,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127736852</v>
+        <v>127736858</v>
       </c>
       <c r="B49" t="n">
-        <v>105418</v>
+        <v>98492</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5455,34 +5455,38 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221141</v>
+        <v>219847</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>595490</v>
+        <v>595407</v>
       </c>
       <c r="R49" t="n">
-        <v>6290176</v>
+        <v>6290191</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5541,10 +5545,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127736858</v>
+        <v>127736852</v>
       </c>
       <c r="B50" t="n">
-        <v>98491</v>
+        <v>105419</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5552,38 +5556,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219847</v>
+        <v>221141</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>595407</v>
+        <v>595490</v>
       </c>
       <c r="R50" t="n">
-        <v>6290191</v>
+        <v>6290176</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5645,7 +5645,7 @@
         <v>127736723</v>
       </c>
       <c r="B51" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>127736736</v>
       </c>
       <c r="B52" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>127736833</v>
       </c>
       <c r="B53" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>127736727</v>
       </c>
       <c r="B54" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>127736717</v>
       </c>
       <c r="B55" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6147,10 +6147,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127736866</v>
+        <v>127736826</v>
       </c>
       <c r="B56" t="n">
-        <v>110562</v>
+        <v>98386</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6158,34 +6158,38 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219711</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>595318</v>
+        <v>595215</v>
       </c>
       <c r="R56" t="n">
-        <v>6290207</v>
+        <v>6290279</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6244,10 +6248,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127736826</v>
+        <v>127736726</v>
       </c>
       <c r="B57" t="n">
-        <v>98385</v>
+        <v>98447</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6255,26 +6259,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6283,10 +6287,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>595215</v>
+        <v>595419</v>
       </c>
       <c r="R57" t="n">
-        <v>6290279</v>
+        <v>6290207</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6313,12 +6317,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6345,10 +6349,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127736726</v>
+        <v>127736866</v>
       </c>
       <c r="B58" t="n">
-        <v>98446</v>
+        <v>110563</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6356,35 +6360,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>595419</v>
+        <v>595318</v>
       </c>
       <c r="R58" t="n">
         <v>6290207</v>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6449,7 +6449,7 @@
         <v>127736871</v>
       </c>
       <c r="B59" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>127736840</v>
       </c>
       <c r="B60" t="n">
-        <v>105418</v>
+        <v>105419</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6640,10 +6640,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127736856</v>
+        <v>127736835</v>
       </c>
       <c r="B61" t="n">
-        <v>105418</v>
+        <v>105419</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>595446</v>
+        <v>595320</v>
       </c>
       <c r="R61" t="n">
-        <v>6290169</v>
+        <v>6290253</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6737,10 +6737,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127736800</v>
+        <v>127736856</v>
       </c>
       <c r="B62" t="n">
-        <v>105418</v>
+        <v>105419</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>595399</v>
+        <v>595446</v>
       </c>
       <c r="R62" t="n">
-        <v>6290260</v>
+        <v>6290169</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6834,10 +6834,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127736854</v>
+        <v>127736800</v>
       </c>
       <c r="B63" t="n">
-        <v>102972</v>
+        <v>105419</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6845,16 +6845,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222002</v>
+        <v>221141</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>595486</v>
+        <v>595399</v>
       </c>
       <c r="R63" t="n">
-        <v>6290171</v>
+        <v>6290260</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6931,10 +6931,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127736835</v>
+        <v>127736854</v>
       </c>
       <c r="B64" t="n">
-        <v>105418</v>
+        <v>102973</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6942,16 +6942,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221141</v>
+        <v>222002</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>595320</v>
+        <v>595486</v>
       </c>
       <c r="R64" t="n">
-        <v>6290253</v>
+        <v>6290171</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7031,7 +7031,7 @@
         <v>127736716</v>
       </c>
       <c r="B65" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>127736838</v>
       </c>
       <c r="B66" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7226,10 +7226,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127736870</v>
+        <v>127736853</v>
       </c>
       <c r="B67" t="n">
-        <v>110562</v>
+        <v>100651</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7237,21 +7237,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7261,10 +7261,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>595272</v>
+        <v>595491</v>
       </c>
       <c r="R67" t="n">
-        <v>6290205</v>
+        <v>6290172</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7323,10 +7323,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127736853</v>
+        <v>127736870</v>
       </c>
       <c r="B68" t="n">
-        <v>100650</v>
+        <v>110563</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7334,21 +7334,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7358,10 +7358,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>595491</v>
+        <v>595272</v>
       </c>
       <c r="R68" t="n">
-        <v>6290172</v>
+        <v>6290205</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127736718</v>
+        <v>127736863</v>
       </c>
       <c r="B69" t="n">
-        <v>98446</v>
+        <v>100651</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7431,38 +7431,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>595293</v>
+        <v>595354</v>
       </c>
       <c r="R69" t="n">
-        <v>6290204</v>
+        <v>6290194</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7489,12 +7485,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7521,10 +7517,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127736865</v>
+        <v>127736718</v>
       </c>
       <c r="B70" t="n">
-        <v>105418</v>
+        <v>98447</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7532,34 +7528,38 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221141</v>
+        <v>219798</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>595335</v>
+        <v>595293</v>
       </c>
       <c r="R70" t="n">
-        <v>6290212</v>
+        <v>6290204</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7586,12 +7586,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7618,10 +7618,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127736837</v>
+        <v>127736865</v>
       </c>
       <c r="B71" t="n">
-        <v>105418</v>
+        <v>105419</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7653,10 +7653,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>595371</v>
+        <v>595335</v>
       </c>
       <c r="R71" t="n">
-        <v>6290254</v>
+        <v>6290212</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7715,10 +7715,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127736863</v>
+        <v>127736837</v>
       </c>
       <c r="B72" t="n">
-        <v>100650</v>
+        <v>105419</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7726,21 +7726,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7750,10 +7750,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>595354</v>
+        <v>595371</v>
       </c>
       <c r="R72" t="n">
-        <v>6290194</v>
+        <v>6290254</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3087,7 +3087,7 @@
         <v>127736872</v>
       </c>
       <c r="B25" t="n">
-        <v>105419</v>
+        <v>105420</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>127736831</v>
       </c>
       <c r="B26" t="n">
-        <v>105419</v>
+        <v>105420</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>127736867</v>
       </c>
       <c r="B27" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3375,10 +3375,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127736857</v>
+        <v>127736860</v>
       </c>
       <c r="B28" t="n">
-        <v>100651</v>
+        <v>105420</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3386,21 +3386,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595446</v>
+        <v>595397</v>
       </c>
       <c r="R28" t="n">
-        <v>6290169</v>
+        <v>6290188</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127736860</v>
+        <v>127736857</v>
       </c>
       <c r="B29" t="n">
-        <v>105419</v>
+        <v>100652</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3483,21 +3483,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595397</v>
+        <v>595446</v>
       </c>
       <c r="R29" t="n">
-        <v>6290188</v>
+        <v>6290169</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3572,7 +3572,7 @@
         <v>127736844</v>
       </c>
       <c r="B30" t="n">
-        <v>105419</v>
+        <v>105420</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>127736859</v>
       </c>
       <c r="B31" t="n">
-        <v>98387</v>
+        <v>98388</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>127736721</v>
       </c>
       <c r="B32" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>127736842</v>
       </c>
       <c r="B33" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>127736715</v>
       </c>
       <c r="B34" t="n">
-        <v>95549</v>
+        <v>95550</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>127736851</v>
       </c>
       <c r="B35" t="n">
-        <v>98491</v>
+        <v>98492</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>127736719</v>
       </c>
       <c r="B36" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127736848</v>
+        <v>127736861</v>
       </c>
       <c r="B37" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595470</v>
+        <v>595396</v>
       </c>
       <c r="R37" t="n">
-        <v>6290237</v>
+        <v>6290191</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4361,10 +4361,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127736861</v>
+        <v>127736848</v>
       </c>
       <c r="B38" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>595396</v>
+        <v>595470</v>
       </c>
       <c r="R38" t="n">
-        <v>6290191</v>
+        <v>6290237</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4458,10 +4458,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127736832</v>
+        <v>127736724</v>
       </c>
       <c r="B39" t="n">
-        <v>100651</v>
+        <v>98445</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4469,34 +4469,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>219797</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>595287</v>
+        <v>595326</v>
       </c>
       <c r="R39" t="n">
-        <v>6290259</v>
+        <v>6290257</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4523,12 +4527,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4555,10 +4559,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127736724</v>
+        <v>127736832</v>
       </c>
       <c r="B40" t="n">
-        <v>98444</v>
+        <v>100652</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4566,38 +4570,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219797</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>595326</v>
+        <v>595287</v>
       </c>
       <c r="R40" t="n">
-        <v>6290257</v>
+        <v>6290259</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4656,10 +4656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127736725</v>
+        <v>127736827</v>
       </c>
       <c r="B41" t="n">
-        <v>98447</v>
+        <v>100652</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4667,38 +4667,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>595345</v>
+        <v>595214</v>
       </c>
       <c r="R41" t="n">
-        <v>6290259</v>
+        <v>6290272</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4725,12 +4721,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4757,10 +4753,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127736855</v>
+        <v>127736836</v>
       </c>
       <c r="B42" t="n">
-        <v>110563</v>
+        <v>100652</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4768,21 +4764,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4792,10 +4788,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>595472</v>
+        <v>595321</v>
       </c>
       <c r="R42" t="n">
-        <v>6290168</v>
+        <v>6290251</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4854,10 +4850,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127736836</v>
+        <v>127736855</v>
       </c>
       <c r="B43" t="n">
-        <v>100651</v>
+        <v>110564</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4865,21 +4861,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4889,10 +4885,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>595321</v>
+        <v>595472</v>
       </c>
       <c r="R43" t="n">
-        <v>6290251</v>
+        <v>6290168</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4951,10 +4947,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127736827</v>
+        <v>127736725</v>
       </c>
       <c r="B44" t="n">
-        <v>100651</v>
+        <v>98448</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4962,34 +4958,38 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>595214</v>
+        <v>595345</v>
       </c>
       <c r="R44" t="n">
-        <v>6290272</v>
+        <v>6290259</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5016,12 +5016,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5051,7 +5051,7 @@
         <v>127736737</v>
       </c>
       <c r="B45" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127736720</v>
+        <v>127736846</v>
       </c>
       <c r="B46" t="n">
-        <v>98447</v>
+        <v>110564</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5160,38 +5160,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>595305</v>
+        <v>595473</v>
       </c>
       <c r="R46" t="n">
-        <v>6290257</v>
+        <v>6290238</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5218,12 +5214,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5250,10 +5246,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127736846</v>
+        <v>127736720</v>
       </c>
       <c r="B47" t="n">
-        <v>110563</v>
+        <v>98448</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5261,34 +5257,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>595473</v>
+        <v>595305</v>
       </c>
       <c r="R47" t="n">
-        <v>6290238</v>
+        <v>6290257</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5350,7 +5350,7 @@
         <v>127736874</v>
       </c>
       <c r="B48" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5444,10 +5444,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127736858</v>
+        <v>127736852</v>
       </c>
       <c r="B49" t="n">
-        <v>98492</v>
+        <v>105420</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5455,38 +5455,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219847</v>
+        <v>221141</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>595407</v>
+        <v>595490</v>
       </c>
       <c r="R49" t="n">
-        <v>6290191</v>
+        <v>6290176</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5545,10 +5541,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127736852</v>
+        <v>127736858</v>
       </c>
       <c r="B50" t="n">
-        <v>105419</v>
+        <v>98493</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5556,34 +5552,38 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221141</v>
+        <v>219847</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>595490</v>
+        <v>595407</v>
       </c>
       <c r="R50" t="n">
-        <v>6290176</v>
+        <v>6290191</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5645,7 +5645,7 @@
         <v>127736723</v>
       </c>
       <c r="B51" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>127736736</v>
       </c>
       <c r="B52" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>127736833</v>
       </c>
       <c r="B53" t="n">
-        <v>98491</v>
+        <v>98492</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>127736727</v>
       </c>
       <c r="B54" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>127736717</v>
       </c>
       <c r="B55" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6147,10 +6147,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127736826</v>
+        <v>127736866</v>
       </c>
       <c r="B56" t="n">
-        <v>98386</v>
+        <v>110564</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6158,38 +6158,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>219711</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>595215</v>
+        <v>595318</v>
       </c>
       <c r="R56" t="n">
-        <v>6290279</v>
+        <v>6290207</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6248,10 +6244,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127736726</v>
+        <v>127736826</v>
       </c>
       <c r="B57" t="n">
-        <v>98447</v>
+        <v>98387</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6259,26 +6255,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219798</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6287,10 +6283,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>595419</v>
+        <v>595215</v>
       </c>
       <c r="R57" t="n">
-        <v>6290207</v>
+        <v>6290279</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6317,12 +6313,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6349,10 +6345,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127736866</v>
+        <v>127736726</v>
       </c>
       <c r="B58" t="n">
-        <v>110563</v>
+        <v>98448</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6360,31 +6356,35 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>595318</v>
+        <v>595419</v>
       </c>
       <c r="R58" t="n">
         <v>6290207</v>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6449,7 +6449,7 @@
         <v>127736871</v>
       </c>
       <c r="B59" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>127736840</v>
       </c>
       <c r="B60" t="n">
-        <v>105419</v>
+        <v>105420</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>127736835</v>
       </c>
       <c r="B61" t="n">
-        <v>105419</v>
+        <v>105420</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>127736856</v>
       </c>
       <c r="B62" t="n">
-        <v>105419</v>
+        <v>105420</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>127736800</v>
       </c>
       <c r="B63" t="n">
-        <v>105419</v>
+        <v>105420</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>127736854</v>
       </c>
       <c r="B64" t="n">
-        <v>102973</v>
+        <v>102974</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>127736716</v>
       </c>
       <c r="B65" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>127736838</v>
       </c>
       <c r="B66" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7226,10 +7226,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127736853</v>
+        <v>127736870</v>
       </c>
       <c r="B67" t="n">
-        <v>100651</v>
+        <v>110564</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7237,21 +7237,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7261,10 +7261,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>595491</v>
+        <v>595272</v>
       </c>
       <c r="R67" t="n">
-        <v>6290172</v>
+        <v>6290205</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7323,10 +7323,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127736870</v>
+        <v>127736853</v>
       </c>
       <c r="B68" t="n">
-        <v>110563</v>
+        <v>100652</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7334,21 +7334,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7358,10 +7358,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>595272</v>
+        <v>595491</v>
       </c>
       <c r="R68" t="n">
-        <v>6290205</v>
+        <v>6290172</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127736863</v>
+        <v>127736865</v>
       </c>
       <c r="B69" t="n">
-        <v>100651</v>
+        <v>105420</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7431,21 +7431,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7455,10 +7455,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>595354</v>
+        <v>595335</v>
       </c>
       <c r="R69" t="n">
-        <v>6290194</v>
+        <v>6290212</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7517,10 +7517,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127736718</v>
+        <v>127736837</v>
       </c>
       <c r="B70" t="n">
-        <v>98447</v>
+        <v>105420</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7528,38 +7528,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219798</v>
+        <v>221141</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>595293</v>
+        <v>595371</v>
       </c>
       <c r="R70" t="n">
-        <v>6290204</v>
+        <v>6290254</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7586,12 +7582,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7618,10 +7614,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127736865</v>
+        <v>127736718</v>
       </c>
       <c r="B71" t="n">
-        <v>105419</v>
+        <v>98448</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7629,34 +7625,38 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221141</v>
+        <v>219798</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>595335</v>
+        <v>595293</v>
       </c>
       <c r="R71" t="n">
-        <v>6290212</v>
+        <v>6290204</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7683,12 +7683,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7715,10 +7715,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127736837</v>
+        <v>127736863</v>
       </c>
       <c r="B72" t="n">
-        <v>105419</v>
+        <v>100652</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7726,21 +7726,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7750,10 +7750,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>595371</v>
+        <v>595354</v>
       </c>
       <c r="R72" t="n">
-        <v>6290254</v>
+        <v>6290194</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3965,10 +3965,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127736715</v>
+        <v>127736851</v>
       </c>
       <c r="B34" t="n">
-        <v>95550</v>
+        <v>98492</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,34 +3976,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2676</v>
+        <v>219862</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>595213</v>
+        <v>595488</v>
       </c>
       <c r="R34" t="n">
-        <v>6290222</v>
+        <v>6290180</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4030,12 +4034,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4062,10 +4066,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127736851</v>
+        <v>127736719</v>
       </c>
       <c r="B35" t="n">
-        <v>98492</v>
+        <v>98448</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4073,21 +4077,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4101,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595488</v>
+        <v>595245</v>
       </c>
       <c r="R35" t="n">
-        <v>6290180</v>
+        <v>6290215</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4131,12 +4135,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4163,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127736719</v>
+        <v>127736848</v>
       </c>
       <c r="B36" t="n">
-        <v>98448</v>
+        <v>100652</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4174,38 +4178,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595245</v>
+        <v>595470</v>
       </c>
       <c r="R36" t="n">
-        <v>6290215</v>
+        <v>6290237</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4232,12 +4232,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4361,10 +4361,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127736848</v>
+        <v>127736715</v>
       </c>
       <c r="B38" t="n">
-        <v>100652</v>
+        <v>95550</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4372,21 +4372,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>2676</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>595470</v>
+        <v>595213</v>
       </c>
       <c r="R38" t="n">
-        <v>6290237</v>
+        <v>6290222</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4458,10 +4458,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127736724</v>
+        <v>127736832</v>
       </c>
       <c r="B39" t="n">
-        <v>98445</v>
+        <v>100652</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4469,38 +4469,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219797</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>595326</v>
+        <v>595287</v>
       </c>
       <c r="R39" t="n">
-        <v>6290257</v>
+        <v>6290259</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4527,12 +4523,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4559,10 +4555,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127736832</v>
+        <v>127736724</v>
       </c>
       <c r="B40" t="n">
-        <v>100652</v>
+        <v>98445</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4570,34 +4566,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>219797</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>595287</v>
+        <v>595326</v>
       </c>
       <c r="R40" t="n">
-        <v>6290259</v>
+        <v>6290257</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4656,7 +4656,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127736827</v>
+        <v>127736836</v>
       </c>
       <c r="B41" t="n">
         <v>100652</v>
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>595214</v>
+        <v>595321</v>
       </c>
       <c r="R41" t="n">
-        <v>6290272</v>
+        <v>6290251</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4753,7 +4753,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127736836</v>
+        <v>127736827</v>
       </c>
       <c r="B42" t="n">
         <v>100652</v>
@@ -4788,10 +4788,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>595321</v>
+        <v>595214</v>
       </c>
       <c r="R42" t="n">
-        <v>6290251</v>
+        <v>6290272</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127736846</v>
+        <v>127736720</v>
       </c>
       <c r="B46" t="n">
-        <v>110564</v>
+        <v>98448</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5160,34 +5160,38 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>595473</v>
+        <v>595305</v>
       </c>
       <c r="R46" t="n">
-        <v>6290238</v>
+        <v>6290257</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5214,12 +5218,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5246,10 +5250,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127736720</v>
+        <v>127736874</v>
       </c>
       <c r="B47" t="n">
-        <v>98448</v>
+        <v>100652</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5257,38 +5261,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>595305</v>
+        <v>595234</v>
       </c>
       <c r="R47" t="n">
-        <v>6290257</v>
+        <v>6290231</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5347,10 +5347,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127736874</v>
+        <v>127736846</v>
       </c>
       <c r="B48" t="n">
-        <v>100652</v>
+        <v>110564</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5358,21 +5358,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>595234</v>
+        <v>595473</v>
       </c>
       <c r="R48" t="n">
-        <v>6290231</v>
+        <v>6290238</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5642,7 +5642,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127736723</v>
+        <v>127736736</v>
       </c>
       <c r="B51" t="n">
         <v>98448</v>
@@ -5681,10 +5681,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>595311</v>
+        <v>595312</v>
       </c>
       <c r="R51" t="n">
-        <v>6290257</v>
+        <v>6290265</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5743,7 +5743,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127736736</v>
+        <v>127736723</v>
       </c>
       <c r="B52" t="n">
         <v>98448</v>
@@ -5782,10 +5782,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>595312</v>
+        <v>595311</v>
       </c>
       <c r="R52" t="n">
-        <v>6290265</v>
+        <v>6290257</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5945,10 +5945,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127736727</v>
+        <v>127736866</v>
       </c>
       <c r="B54" t="n">
-        <v>98448</v>
+        <v>110564</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5956,38 +5956,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>595482</v>
+        <v>595318</v>
       </c>
       <c r="R54" t="n">
-        <v>6290215</v>
+        <v>6290207</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6014,12 +6010,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6046,7 +6042,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127736717</v>
+        <v>127736726</v>
       </c>
       <c r="B55" t="n">
         <v>98448</v>
@@ -6076,7 +6072,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6085,10 +6081,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>595312</v>
+        <v>595419</v>
       </c>
       <c r="R55" t="n">
-        <v>6290198</v>
+        <v>6290207</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6147,10 +6143,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127736866</v>
+        <v>127736826</v>
       </c>
       <c r="B56" t="n">
-        <v>110564</v>
+        <v>98387</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6158,34 +6154,38 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219711</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>595318</v>
+        <v>595215</v>
       </c>
       <c r="R56" t="n">
-        <v>6290207</v>
+        <v>6290279</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127736826</v>
+        <v>127736727</v>
       </c>
       <c r="B57" t="n">
-        <v>98387</v>
+        <v>98448</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6255,26 +6255,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>595215</v>
+        <v>595482</v>
       </c>
       <c r="R57" t="n">
-        <v>6290279</v>
+        <v>6290215</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6313,12 +6313,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6345,7 +6345,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127736726</v>
+        <v>127736717</v>
       </c>
       <c r="B58" t="n">
         <v>98448</v>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>595419</v>
+        <v>595312</v>
       </c>
       <c r="R58" t="n">
-        <v>6290207</v>
+        <v>6290198</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6543,10 +6543,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127736840</v>
+        <v>127736854</v>
       </c>
       <c r="B60" t="n">
-        <v>105420</v>
+        <v>102974</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6554,16 +6554,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221141</v>
+        <v>222002</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>595387</v>
+        <v>595486</v>
       </c>
       <c r="R60" t="n">
-        <v>6290227</v>
+        <v>6290171</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6640,7 +6640,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127736835</v>
+        <v>127736840</v>
       </c>
       <c r="B61" t="n">
         <v>105420</v>
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>595320</v>
+        <v>595387</v>
       </c>
       <c r="R61" t="n">
-        <v>6290253</v>
+        <v>6290227</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6834,7 +6834,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127736800</v>
+        <v>127736835</v>
       </c>
       <c r="B63" t="n">
         <v>105420</v>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>595399</v>
+        <v>595320</v>
       </c>
       <c r="R63" t="n">
-        <v>6290260</v>
+        <v>6290253</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6931,10 +6931,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127736854</v>
+        <v>127736800</v>
       </c>
       <c r="B64" t="n">
-        <v>102974</v>
+        <v>105420</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6942,16 +6942,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222002</v>
+        <v>221141</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>595486</v>
+        <v>595399</v>
       </c>
       <c r="R64" t="n">
-        <v>6290171</v>
+        <v>6290260</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127736865</v>
+        <v>127736718</v>
       </c>
       <c r="B69" t="n">
-        <v>105420</v>
+        <v>98448</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7431,34 +7431,38 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221141</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>595335</v>
+        <v>595293</v>
       </c>
       <c r="R69" t="n">
-        <v>6290212</v>
+        <v>6290204</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7485,12 +7489,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7517,7 +7521,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127736837</v>
+        <v>127736865</v>
       </c>
       <c r="B70" t="n">
         <v>105420</v>
@@ -7552,10 +7556,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>595371</v>
+        <v>595335</v>
       </c>
       <c r="R70" t="n">
-        <v>6290254</v>
+        <v>6290212</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7614,10 +7618,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127736718</v>
+        <v>127736837</v>
       </c>
       <c r="B71" t="n">
-        <v>98448</v>
+        <v>105420</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7625,38 +7629,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219798</v>
+        <v>221141</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>595293</v>
+        <v>595371</v>
       </c>
       <c r="R71" t="n">
-        <v>6290204</v>
+        <v>6290254</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7683,12 +7683,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -5642,7 +5642,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127736736</v>
+        <v>127736723</v>
       </c>
       <c r="B51" t="n">
         <v>98448</v>
@@ -5681,10 +5681,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>595312</v>
+        <v>595311</v>
       </c>
       <c r="R51" t="n">
-        <v>6290265</v>
+        <v>6290257</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5743,7 +5743,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127736723</v>
+        <v>127736736</v>
       </c>
       <c r="B52" t="n">
         <v>98448</v>
@@ -5782,10 +5782,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>595311</v>
+        <v>595312</v>
       </c>
       <c r="R52" t="n">
-        <v>6290257</v>
+        <v>6290265</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6737,7 +6737,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127736856</v>
+        <v>127736835</v>
       </c>
       <c r="B62" t="n">
         <v>105420</v>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>595446</v>
+        <v>595320</v>
       </c>
       <c r="R62" t="n">
-        <v>6290169</v>
+        <v>6290253</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6834,7 +6834,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127736835</v>
+        <v>127736856</v>
       </c>
       <c r="B63" t="n">
         <v>105420</v>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>595320</v>
+        <v>595446</v>
       </c>
       <c r="R63" t="n">
-        <v>6290253</v>
+        <v>6290169</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3965,10 +3965,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127736851</v>
+        <v>127736848</v>
       </c>
       <c r="B34" t="n">
-        <v>98492</v>
+        <v>100652</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,38 +3976,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>595488</v>
+        <v>595470</v>
       </c>
       <c r="R34" t="n">
-        <v>6290180</v>
+        <v>6290237</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,10 +4062,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127736719</v>
+        <v>127736861</v>
       </c>
       <c r="B35" t="n">
-        <v>98448</v>
+        <v>100652</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4077,38 +4073,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595245</v>
+        <v>595396</v>
       </c>
       <c r="R35" t="n">
-        <v>6290215</v>
+        <v>6290191</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4135,12 +4127,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4167,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127736848</v>
+        <v>127736715</v>
       </c>
       <c r="B36" t="n">
-        <v>100652</v>
+        <v>95550</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4178,21 +4170,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>2676</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4202,10 +4194,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595470</v>
+        <v>595213</v>
       </c>
       <c r="R36" t="n">
-        <v>6290237</v>
+        <v>6290222</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4232,12 +4224,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4264,10 +4256,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127736861</v>
+        <v>127736851</v>
       </c>
       <c r="B37" t="n">
-        <v>100652</v>
+        <v>98492</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4275,34 +4267,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595396</v>
+        <v>595488</v>
       </c>
       <c r="R37" t="n">
-        <v>6290191</v>
+        <v>6290180</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4361,10 +4357,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127736715</v>
+        <v>127736719</v>
       </c>
       <c r="B38" t="n">
-        <v>95550</v>
+        <v>98448</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4372,34 +4368,38 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2676</v>
+        <v>219798</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>595213</v>
+        <v>595245</v>
       </c>
       <c r="R38" t="n">
-        <v>6290222</v>
+        <v>6290215</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5048,10 +5048,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127736737</v>
+        <v>127736846</v>
       </c>
       <c r="B45" t="n">
-        <v>98448</v>
+        <v>110564</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5059,38 +5059,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>595256</v>
+        <v>595473</v>
       </c>
       <c r="R45" t="n">
-        <v>6290277</v>
+        <v>6290238</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5117,12 +5113,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5149,7 +5145,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127736720</v>
+        <v>127736737</v>
       </c>
       <c r="B46" t="n">
         <v>98448</v>
@@ -5179,7 +5175,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5188,10 +5184,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>595305</v>
+        <v>595256</v>
       </c>
       <c r="R46" t="n">
-        <v>6290257</v>
+        <v>6290277</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5250,10 +5246,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127736874</v>
+        <v>127736720</v>
       </c>
       <c r="B47" t="n">
-        <v>100652</v>
+        <v>98448</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5261,34 +5257,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>595234</v>
+        <v>595305</v>
       </c>
       <c r="R47" t="n">
-        <v>6290231</v>
+        <v>6290257</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5347,10 +5347,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127736846</v>
+        <v>127736874</v>
       </c>
       <c r="B48" t="n">
-        <v>110564</v>
+        <v>100652</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5358,21 +5358,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>595473</v>
+        <v>595234</v>
       </c>
       <c r="R48" t="n">
-        <v>6290238</v>
+        <v>6290231</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5642,7 +5642,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127736723</v>
+        <v>127736736</v>
       </c>
       <c r="B51" t="n">
         <v>98448</v>
@@ -5681,10 +5681,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>595311</v>
+        <v>595312</v>
       </c>
       <c r="R51" t="n">
-        <v>6290257</v>
+        <v>6290265</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5743,7 +5743,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127736736</v>
+        <v>127736723</v>
       </c>
       <c r="B52" t="n">
         <v>98448</v>
@@ -5782,10 +5782,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>595312</v>
+        <v>595311</v>
       </c>
       <c r="R52" t="n">
-        <v>6290265</v>
+        <v>6290257</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6737,7 +6737,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127736835</v>
+        <v>127736856</v>
       </c>
       <c r="B62" t="n">
         <v>105420</v>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>595320</v>
+        <v>595446</v>
       </c>
       <c r="R62" t="n">
-        <v>6290253</v>
+        <v>6290169</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6834,7 +6834,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127736856</v>
+        <v>127736835</v>
       </c>
       <c r="B63" t="n">
         <v>105420</v>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>595446</v>
+        <v>595320</v>
       </c>
       <c r="R63" t="n">
-        <v>6290169</v>
+        <v>6290253</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127736718</v>
+        <v>127736865</v>
       </c>
       <c r="B69" t="n">
-        <v>98448</v>
+        <v>105420</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7431,38 +7431,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>221141</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>595293</v>
+        <v>595335</v>
       </c>
       <c r="R69" t="n">
-        <v>6290204</v>
+        <v>6290212</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7489,12 +7485,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7521,7 +7517,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127736865</v>
+        <v>127736837</v>
       </c>
       <c r="B70" t="n">
         <v>105420</v>
@@ -7556,10 +7552,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>595335</v>
+        <v>595371</v>
       </c>
       <c r="R70" t="n">
-        <v>6290212</v>
+        <v>6290254</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7618,10 +7614,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127736837</v>
+        <v>127736718</v>
       </c>
       <c r="B71" t="n">
-        <v>105420</v>
+        <v>98448</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7629,34 +7625,38 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221141</v>
+        <v>219798</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>595371</v>
+        <v>595293</v>
       </c>
       <c r="R71" t="n">
-        <v>6290254</v>
+        <v>6290204</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7683,12 +7683,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -5048,10 +5048,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127736846</v>
+        <v>127736737</v>
       </c>
       <c r="B45" t="n">
-        <v>110564</v>
+        <v>98448</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5059,34 +5059,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>595473</v>
+        <v>595256</v>
       </c>
       <c r="R45" t="n">
-        <v>6290238</v>
+        <v>6290277</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5113,12 +5117,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5145,7 +5149,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127736737</v>
+        <v>127736720</v>
       </c>
       <c r="B46" t="n">
         <v>98448</v>
@@ -5175,7 +5179,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5184,10 +5188,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>595256</v>
+        <v>595305</v>
       </c>
       <c r="R46" t="n">
-        <v>6290277</v>
+        <v>6290257</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5246,10 +5250,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127736720</v>
+        <v>127736874</v>
       </c>
       <c r="B47" t="n">
-        <v>98448</v>
+        <v>100652</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5257,38 +5261,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>595305</v>
+        <v>595234</v>
       </c>
       <c r="R47" t="n">
-        <v>6290257</v>
+        <v>6290231</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5347,10 +5347,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127736874</v>
+        <v>127736846</v>
       </c>
       <c r="B48" t="n">
-        <v>100652</v>
+        <v>110564</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5358,21 +5358,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>595234</v>
+        <v>595473</v>
       </c>
       <c r="R48" t="n">
-        <v>6290231</v>
+        <v>6290238</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127736865</v>
+        <v>127736718</v>
       </c>
       <c r="B69" t="n">
-        <v>105420</v>
+        <v>98448</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7431,34 +7431,38 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221141</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>595335</v>
+        <v>595293</v>
       </c>
       <c r="R69" t="n">
-        <v>6290212</v>
+        <v>6290204</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7485,12 +7489,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7517,7 +7521,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127736837</v>
+        <v>127736865</v>
       </c>
       <c r="B70" t="n">
         <v>105420</v>
@@ -7552,10 +7556,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>595371</v>
+        <v>595335</v>
       </c>
       <c r="R70" t="n">
-        <v>6290254</v>
+        <v>6290212</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7614,10 +7618,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127736718</v>
+        <v>127736837</v>
       </c>
       <c r="B71" t="n">
-        <v>98448</v>
+        <v>105420</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7625,38 +7629,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219798</v>
+        <v>221141</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>595293</v>
+        <v>595371</v>
       </c>
       <c r="R71" t="n">
-        <v>6290204</v>
+        <v>6290254</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7683,12 +7683,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -4656,10 +4656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127736836</v>
+        <v>127736855</v>
       </c>
       <c r="B41" t="n">
-        <v>100652</v>
+        <v>110564</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4667,21 +4667,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>595321</v>
+        <v>595472</v>
       </c>
       <c r="R41" t="n">
-        <v>6290251</v>
+        <v>6290168</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4753,10 +4753,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127736827</v>
+        <v>127736725</v>
       </c>
       <c r="B42" t="n">
-        <v>100652</v>
+        <v>98448</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4764,34 +4764,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>595214</v>
+        <v>595345</v>
       </c>
       <c r="R42" t="n">
-        <v>6290272</v>
+        <v>6290259</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4818,12 +4822,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4850,10 +4854,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127736855</v>
+        <v>127736836</v>
       </c>
       <c r="B43" t="n">
-        <v>110564</v>
+        <v>100652</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4861,21 +4865,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4885,10 +4889,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>595472</v>
+        <v>595321</v>
       </c>
       <c r="R43" t="n">
-        <v>6290168</v>
+        <v>6290251</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4947,10 +4951,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127736725</v>
+        <v>127736827</v>
       </c>
       <c r="B44" t="n">
-        <v>98448</v>
+        <v>100652</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4958,38 +4962,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>595345</v>
+        <v>595214</v>
       </c>
       <c r="R44" t="n">
-        <v>6290259</v>
+        <v>6290272</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5016,12 +5016,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5642,7 +5642,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127736736</v>
+        <v>127736723</v>
       </c>
       <c r="B51" t="n">
         <v>98448</v>
@@ -5681,10 +5681,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>595312</v>
+        <v>595311</v>
       </c>
       <c r="R51" t="n">
-        <v>6290265</v>
+        <v>6290257</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5743,7 +5743,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127736723</v>
+        <v>127736736</v>
       </c>
       <c r="B52" t="n">
         <v>98448</v>
@@ -5782,10 +5782,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>595311</v>
+        <v>595312</v>
       </c>
       <c r="R52" t="n">
-        <v>6290257</v>
+        <v>6290265</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6737,7 +6737,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127736856</v>
+        <v>127736835</v>
       </c>
       <c r="B62" t="n">
         <v>105420</v>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>595446</v>
+        <v>595320</v>
       </c>
       <c r="R62" t="n">
-        <v>6290169</v>
+        <v>6290253</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6834,7 +6834,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127736835</v>
+        <v>127736856</v>
       </c>
       <c r="B63" t="n">
         <v>105420</v>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>595320</v>
+        <v>595446</v>
       </c>
       <c r="R63" t="n">
-        <v>6290253</v>
+        <v>6290169</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -5048,10 +5048,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127736737</v>
+        <v>127736846</v>
       </c>
       <c r="B45" t="n">
-        <v>98448</v>
+        <v>110564</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5059,38 +5059,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>595256</v>
+        <v>595473</v>
       </c>
       <c r="R45" t="n">
-        <v>6290277</v>
+        <v>6290238</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5117,12 +5113,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5149,7 +5145,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127736720</v>
+        <v>127736737</v>
       </c>
       <c r="B46" t="n">
         <v>98448</v>
@@ -5179,7 +5175,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5188,10 +5184,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>595305</v>
+        <v>595256</v>
       </c>
       <c r="R46" t="n">
-        <v>6290257</v>
+        <v>6290277</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5250,10 +5246,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127736874</v>
+        <v>127736720</v>
       </c>
       <c r="B47" t="n">
-        <v>100652</v>
+        <v>98448</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5261,34 +5257,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>595234</v>
+        <v>595305</v>
       </c>
       <c r="R47" t="n">
-        <v>6290231</v>
+        <v>6290257</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5347,10 +5347,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127736846</v>
+        <v>127736874</v>
       </c>
       <c r="B48" t="n">
-        <v>110564</v>
+        <v>100652</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5358,21 +5358,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>595473</v>
+        <v>595234</v>
       </c>
       <c r="R48" t="n">
-        <v>6290238</v>
+        <v>6290231</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127736718</v>
+        <v>127736865</v>
       </c>
       <c r="B69" t="n">
-        <v>98448</v>
+        <v>105420</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7431,38 +7431,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>221141</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>595293</v>
+        <v>595335</v>
       </c>
       <c r="R69" t="n">
-        <v>6290204</v>
+        <v>6290212</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7489,12 +7485,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7521,7 +7517,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127736865</v>
+        <v>127736837</v>
       </c>
       <c r="B70" t="n">
         <v>105420</v>
@@ -7556,10 +7552,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>595335</v>
+        <v>595371</v>
       </c>
       <c r="R70" t="n">
-        <v>6290212</v>
+        <v>6290254</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7618,10 +7614,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127736837</v>
+        <v>127736718</v>
       </c>
       <c r="B71" t="n">
-        <v>105420</v>
+        <v>98448</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7629,34 +7625,38 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221141</v>
+        <v>219798</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>595371</v>
+        <v>595293</v>
       </c>
       <c r="R71" t="n">
-        <v>6290254</v>
+        <v>6290204</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7683,12 +7683,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -5642,7 +5642,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127736723</v>
+        <v>127736736</v>
       </c>
       <c r="B51" t="n">
         <v>98448</v>
@@ -5681,10 +5681,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>595311</v>
+        <v>595312</v>
       </c>
       <c r="R51" t="n">
-        <v>6290257</v>
+        <v>6290265</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5743,7 +5743,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127736736</v>
+        <v>127736723</v>
       </c>
       <c r="B52" t="n">
         <v>98448</v>
@@ -5782,10 +5782,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>595312</v>
+        <v>595311</v>
       </c>
       <c r="R52" t="n">
-        <v>6290265</v>
+        <v>6290257</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6737,7 +6737,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127736835</v>
+        <v>127736856</v>
       </c>
       <c r="B62" t="n">
         <v>105420</v>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>595320</v>
+        <v>595446</v>
       </c>
       <c r="R62" t="n">
-        <v>6290253</v>
+        <v>6290169</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6834,7 +6834,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127736856</v>
+        <v>127736835</v>
       </c>
       <c r="B63" t="n">
         <v>105420</v>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>595446</v>
+        <v>595320</v>
       </c>
       <c r="R63" t="n">
-        <v>6290169</v>
+        <v>6290253</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127736865</v>
+        <v>127736718</v>
       </c>
       <c r="B69" t="n">
-        <v>105420</v>
+        <v>98448</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7431,34 +7431,38 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221141</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>595335</v>
+        <v>595293</v>
       </c>
       <c r="R69" t="n">
-        <v>6290212</v>
+        <v>6290204</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7485,12 +7489,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7517,7 +7521,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127736837</v>
+        <v>127736865</v>
       </c>
       <c r="B70" t="n">
         <v>105420</v>
@@ -7552,10 +7556,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>595371</v>
+        <v>595335</v>
       </c>
       <c r="R70" t="n">
-        <v>6290254</v>
+        <v>6290212</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7614,10 +7618,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127736718</v>
+        <v>127736837</v>
       </c>
       <c r="B71" t="n">
-        <v>98448</v>
+        <v>105420</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7625,38 +7629,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219798</v>
+        <v>221141</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>595293</v>
+        <v>595371</v>
       </c>
       <c r="R71" t="n">
-        <v>6290204</v>
+        <v>6290254</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7683,12 +7683,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3087,7 +3087,7 @@
         <v>127736872</v>
       </c>
       <c r="B25" t="n">
-        <v>105420</v>
+        <v>105428</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>127736831</v>
       </c>
       <c r="B26" t="n">
-        <v>105420</v>
+        <v>105428</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>127736867</v>
       </c>
       <c r="B27" t="n">
-        <v>100652</v>
+        <v>100660</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>127736860</v>
       </c>
       <c r="B28" t="n">
-        <v>105420</v>
+        <v>105428</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>127736857</v>
       </c>
       <c r="B29" t="n">
-        <v>100652</v>
+        <v>100660</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>127736844</v>
       </c>
       <c r="B30" t="n">
-        <v>105420</v>
+        <v>105428</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>127736859</v>
       </c>
       <c r="B31" t="n">
-        <v>98388</v>
+        <v>98396</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>127736721</v>
       </c>
       <c r="B32" t="n">
-        <v>98448</v>
+        <v>98456</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>127736842</v>
       </c>
       <c r="B33" t="n">
-        <v>100652</v>
+        <v>100660</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127736848</v>
+        <v>127736851</v>
       </c>
       <c r="B34" t="n">
-        <v>100652</v>
+        <v>98500</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,34 +3976,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>595470</v>
+        <v>595488</v>
       </c>
       <c r="R34" t="n">
-        <v>6290237</v>
+        <v>6290180</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4062,10 +4066,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127736861</v>
+        <v>127736719</v>
       </c>
       <c r="B35" t="n">
-        <v>100652</v>
+        <v>98456</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4073,34 +4077,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595396</v>
+        <v>595245</v>
       </c>
       <c r="R35" t="n">
-        <v>6290191</v>
+        <v>6290215</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4127,12 +4135,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4159,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127736715</v>
+        <v>127736848</v>
       </c>
       <c r="B36" t="n">
-        <v>95550</v>
+        <v>100660</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4170,21 +4178,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2676</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4194,10 +4202,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595213</v>
+        <v>595470</v>
       </c>
       <c r="R36" t="n">
-        <v>6290222</v>
+        <v>6290237</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4224,12 +4232,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4256,10 +4264,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127736851</v>
+        <v>127736861</v>
       </c>
       <c r="B37" t="n">
-        <v>98492</v>
+        <v>100660</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4267,38 +4275,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595488</v>
+        <v>595396</v>
       </c>
       <c r="R37" t="n">
-        <v>6290180</v>
+        <v>6290191</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4357,10 +4361,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127736719</v>
+        <v>127736715</v>
       </c>
       <c r="B38" t="n">
-        <v>98448</v>
+        <v>95558</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4368,38 +4372,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219798</v>
+        <v>2676</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>595245</v>
+        <v>595213</v>
       </c>
       <c r="R38" t="n">
-        <v>6290215</v>
+        <v>6290222</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4461,7 +4461,7 @@
         <v>127736832</v>
       </c>
       <c r="B39" t="n">
-        <v>100652</v>
+        <v>100660</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>127736724</v>
       </c>
       <c r="B40" t="n">
-        <v>98445</v>
+        <v>98453</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>127736855</v>
       </c>
       <c r="B41" t="n">
-        <v>110564</v>
+        <v>110572</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>127736725</v>
       </c>
       <c r="B42" t="n">
-        <v>98448</v>
+        <v>98456</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>127736836</v>
       </c>
       <c r="B43" t="n">
-        <v>100652</v>
+        <v>100660</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>127736827</v>
       </c>
       <c r="B44" t="n">
-        <v>100652</v>
+        <v>100660</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>127736846</v>
       </c>
       <c r="B45" t="n">
-        <v>110564</v>
+        <v>110572</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>127736737</v>
       </c>
       <c r="B46" t="n">
-        <v>98448</v>
+        <v>98456</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>127736720</v>
       </c>
       <c r="B47" t="n">
-        <v>98448</v>
+        <v>98456</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>127736874</v>
       </c>
       <c r="B48" t="n">
-        <v>100652</v>
+        <v>100660</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5444,10 +5444,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127736852</v>
+        <v>127736858</v>
       </c>
       <c r="B49" t="n">
-        <v>105420</v>
+        <v>98501</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5455,34 +5455,38 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221141</v>
+        <v>219847</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>595490</v>
+        <v>595407</v>
       </c>
       <c r="R49" t="n">
-        <v>6290176</v>
+        <v>6290191</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5541,10 +5545,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127736858</v>
+        <v>127736852</v>
       </c>
       <c r="B50" t="n">
-        <v>98493</v>
+        <v>105428</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5552,38 +5556,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219847</v>
+        <v>221141</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>595407</v>
+        <v>595490</v>
       </c>
       <c r="R50" t="n">
-        <v>6290191</v>
+        <v>6290176</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5642,10 +5642,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127736736</v>
+        <v>127736723</v>
       </c>
       <c r="B51" t="n">
-        <v>98448</v>
+        <v>98456</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5681,10 +5681,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>595312</v>
+        <v>595311</v>
       </c>
       <c r="R51" t="n">
-        <v>6290265</v>
+        <v>6290257</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5743,10 +5743,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127736723</v>
+        <v>127736736</v>
       </c>
       <c r="B52" t="n">
-        <v>98448</v>
+        <v>98456</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5782,10 +5782,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>595311</v>
+        <v>595312</v>
       </c>
       <c r="R52" t="n">
-        <v>6290257</v>
+        <v>6290265</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5847,7 +5847,7 @@
         <v>127736833</v>
       </c>
       <c r="B53" t="n">
-        <v>98492</v>
+        <v>98500</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>127736866</v>
       </c>
       <c r="B54" t="n">
-        <v>110564</v>
+        <v>110572</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127736726</v>
+        <v>127736871</v>
       </c>
       <c r="B55" t="n">
-        <v>98448</v>
+        <v>100660</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6053,38 +6053,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>595419</v>
+        <v>595263</v>
       </c>
       <c r="R55" t="n">
-        <v>6290207</v>
+        <v>6290211</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6111,12 +6107,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6143,10 +6139,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127736826</v>
+        <v>127736727</v>
       </c>
       <c r="B56" t="n">
-        <v>98387</v>
+        <v>98456</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6154,26 +6150,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>219798</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6182,10 +6178,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>595215</v>
+        <v>595482</v>
       </c>
       <c r="R56" t="n">
-        <v>6290279</v>
+        <v>6290215</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6212,12 +6208,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6244,10 +6240,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127736727</v>
+        <v>127736717</v>
       </c>
       <c r="B57" t="n">
-        <v>98448</v>
+        <v>98456</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6274,7 +6270,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6283,10 +6279,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>595482</v>
+        <v>595312</v>
       </c>
       <c r="R57" t="n">
-        <v>6290215</v>
+        <v>6290198</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6345,10 +6341,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127736717</v>
+        <v>127736826</v>
       </c>
       <c r="B58" t="n">
-        <v>98448</v>
+        <v>98395</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6356,26 +6352,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219798</v>
+        <v>219790</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6384,10 +6380,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>595312</v>
+        <v>595215</v>
       </c>
       <c r="R58" t="n">
-        <v>6290198</v>
+        <v>6290279</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6414,12 +6410,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6446,10 +6442,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127736871</v>
+        <v>127736726</v>
       </c>
       <c r="B59" t="n">
-        <v>100652</v>
+        <v>98456</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6457,34 +6453,38 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>595263</v>
+        <v>595419</v>
       </c>
       <c r="R59" t="n">
-        <v>6290211</v>
+        <v>6290207</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6511,12 +6511,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6546,7 +6546,7 @@
         <v>127736854</v>
       </c>
       <c r="B60" t="n">
-        <v>102974</v>
+        <v>102982</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>127736840</v>
       </c>
       <c r="B61" t="n">
-        <v>105420</v>
+        <v>105428</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6737,10 +6737,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127736856</v>
+        <v>127736835</v>
       </c>
       <c r="B62" t="n">
-        <v>105420</v>
+        <v>105428</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>595446</v>
+        <v>595320</v>
       </c>
       <c r="R62" t="n">
-        <v>6290169</v>
+        <v>6290253</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6834,10 +6834,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127736835</v>
+        <v>127736856</v>
       </c>
       <c r="B63" t="n">
-        <v>105420</v>
+        <v>105428</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>595320</v>
+        <v>595446</v>
       </c>
       <c r="R63" t="n">
-        <v>6290253</v>
+        <v>6290169</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6934,7 +6934,7 @@
         <v>127736800</v>
       </c>
       <c r="B64" t="n">
-        <v>105420</v>
+        <v>105428</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>127736716</v>
       </c>
       <c r="B65" t="n">
-        <v>98448</v>
+        <v>98456</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>127736838</v>
       </c>
       <c r="B66" t="n">
-        <v>100652</v>
+        <v>100660</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>127736870</v>
       </c>
       <c r="B67" t="n">
-        <v>110564</v>
+        <v>110572</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>127736853</v>
       </c>
       <c r="B68" t="n">
-        <v>100652</v>
+        <v>100660</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127736718</v>
+        <v>127736865</v>
       </c>
       <c r="B69" t="n">
-        <v>98448</v>
+        <v>105428</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7431,38 +7431,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>221141</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>595293</v>
+        <v>595335</v>
       </c>
       <c r="R69" t="n">
-        <v>6290204</v>
+        <v>6290212</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7489,12 +7485,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7521,10 +7517,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127736865</v>
+        <v>127736837</v>
       </c>
       <c r="B70" t="n">
-        <v>105420</v>
+        <v>105428</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7556,10 +7552,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>595335</v>
+        <v>595371</v>
       </c>
       <c r="R70" t="n">
-        <v>6290212</v>
+        <v>6290254</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7618,10 +7614,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127736837</v>
+        <v>127736863</v>
       </c>
       <c r="B71" t="n">
-        <v>105420</v>
+        <v>100660</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7629,21 +7625,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7653,10 +7649,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>595371</v>
+        <v>595354</v>
       </c>
       <c r="R71" t="n">
-        <v>6290254</v>
+        <v>6290194</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7715,10 +7711,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127736863</v>
+        <v>127736718</v>
       </c>
       <c r="B72" t="n">
-        <v>100652</v>
+        <v>98456</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7726,34 +7722,38 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>595354</v>
+        <v>595293</v>
       </c>
       <c r="R72" t="n">
-        <v>6290194</v>
+        <v>6290204</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7780,12 +7780,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3965,10 +3965,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127736851</v>
+        <v>127736715</v>
       </c>
       <c r="B34" t="n">
-        <v>98500</v>
+        <v>95558</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,38 +3976,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219862</v>
+        <v>2676</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>595488</v>
+        <v>595213</v>
       </c>
       <c r="R34" t="n">
-        <v>6290180</v>
+        <v>6290222</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4034,12 +4030,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4066,10 +4062,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127736719</v>
+        <v>127736851</v>
       </c>
       <c r="B35" t="n">
-        <v>98456</v>
+        <v>98500</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4077,21 +4073,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4105,10 +4101,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595245</v>
+        <v>595488</v>
       </c>
       <c r="R35" t="n">
-        <v>6290215</v>
+        <v>6290180</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4135,12 +4131,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4167,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127736848</v>
+        <v>127736719</v>
       </c>
       <c r="B36" t="n">
-        <v>100660</v>
+        <v>98456</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4178,34 +4174,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595470</v>
+        <v>595245</v>
       </c>
       <c r="R36" t="n">
-        <v>6290237</v>
+        <v>6290215</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4232,12 +4232,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4264,7 +4264,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127736861</v>
+        <v>127736848</v>
       </c>
       <c r="B37" t="n">
         <v>100660</v>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595396</v>
+        <v>595470</v>
       </c>
       <c r="R37" t="n">
-        <v>6290191</v>
+        <v>6290237</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4361,10 +4361,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127736715</v>
+        <v>127736861</v>
       </c>
       <c r="B38" t="n">
-        <v>95558</v>
+        <v>100660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4372,21 +4372,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2676</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>595213</v>
+        <v>595396</v>
       </c>
       <c r="R38" t="n">
-        <v>6290222</v>
+        <v>6290191</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -7028,10 +7028,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127736716</v>
+        <v>127736838</v>
       </c>
       <c r="B65" t="n">
-        <v>98456</v>
+        <v>100660</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7039,38 +7039,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>595320</v>
+        <v>595371</v>
       </c>
       <c r="R65" t="n">
-        <v>6290193</v>
+        <v>6290254</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7097,12 +7093,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7129,10 +7125,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127736838</v>
+        <v>127736716</v>
       </c>
       <c r="B66" t="n">
-        <v>100660</v>
+        <v>98456</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7140,34 +7136,38 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>595371</v>
+        <v>595320</v>
       </c>
       <c r="R66" t="n">
-        <v>6290254</v>
+        <v>6290193</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7194,12 +7194,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7226,10 +7226,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127736870</v>
+        <v>127736853</v>
       </c>
       <c r="B67" t="n">
-        <v>110572</v>
+        <v>100660</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7237,21 +7237,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7261,10 +7261,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>595272</v>
+        <v>595491</v>
       </c>
       <c r="R67" t="n">
-        <v>6290205</v>
+        <v>6290172</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7323,10 +7323,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127736853</v>
+        <v>127736870</v>
       </c>
       <c r="B68" t="n">
-        <v>100660</v>
+        <v>110572</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7334,21 +7334,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7358,10 +7358,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>595491</v>
+        <v>595272</v>
       </c>
       <c r="R68" t="n">
-        <v>6290172</v>
+        <v>6290205</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127736865</v>
+        <v>127736718</v>
       </c>
       <c r="B69" t="n">
-        <v>105428</v>
+        <v>98456</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7431,34 +7431,38 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221141</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>595335</v>
+        <v>595293</v>
       </c>
       <c r="R69" t="n">
-        <v>6290212</v>
+        <v>6290204</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7485,12 +7489,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7517,7 +7521,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127736837</v>
+        <v>127736865</v>
       </c>
       <c r="B70" t="n">
         <v>105428</v>
@@ -7552,10 +7556,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>595371</v>
+        <v>595335</v>
       </c>
       <c r="R70" t="n">
-        <v>6290254</v>
+        <v>6290212</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7614,10 +7618,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127736863</v>
+        <v>127736837</v>
       </c>
       <c r="B71" t="n">
-        <v>100660</v>
+        <v>105428</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7625,21 +7629,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7649,10 +7653,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>595354</v>
+        <v>595371</v>
       </c>
       <c r="R71" t="n">
-        <v>6290194</v>
+        <v>6290254</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7711,10 +7715,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127736718</v>
+        <v>127736863</v>
       </c>
       <c r="B72" t="n">
-        <v>98456</v>
+        <v>100660</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7722,38 +7726,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>595293</v>
+        <v>595354</v>
       </c>
       <c r="R72" t="n">
-        <v>6290204</v>
+        <v>6290194</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7780,12 +7780,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -3087,7 +3087,7 @@
         <v>127736872</v>
       </c>
       <c r="B25" t="n">
-        <v>105428</v>
+        <v>105521</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>127736831</v>
       </c>
       <c r="B26" t="n">
-        <v>105428</v>
+        <v>105521</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>127736867</v>
       </c>
       <c r="B27" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>127736860</v>
       </c>
       <c r="B28" t="n">
-        <v>105428</v>
+        <v>105521</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>127736857</v>
       </c>
       <c r="B29" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>127736844</v>
       </c>
       <c r="B30" t="n">
-        <v>105428</v>
+        <v>105521</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>127736859</v>
       </c>
       <c r="B31" t="n">
-        <v>98396</v>
+        <v>98489</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>127736721</v>
       </c>
       <c r="B32" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>127736842</v>
       </c>
       <c r="B33" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127736715</v>
+        <v>127736851</v>
       </c>
       <c r="B34" t="n">
-        <v>95558</v>
+        <v>98593</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,34 +3976,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2676</v>
+        <v>219862</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>595213</v>
+        <v>595488</v>
       </c>
       <c r="R34" t="n">
-        <v>6290222</v>
+        <v>6290180</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4030,12 +4034,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4062,10 +4066,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127736851</v>
+        <v>127736719</v>
       </c>
       <c r="B35" t="n">
-        <v>98500</v>
+        <v>98549</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4073,21 +4077,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4101,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595488</v>
+        <v>595245</v>
       </c>
       <c r="R35" t="n">
-        <v>6290180</v>
+        <v>6290215</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4131,12 +4135,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4163,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127736719</v>
+        <v>127736715</v>
       </c>
       <c r="B36" t="n">
-        <v>98456</v>
+        <v>95651</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4174,38 +4178,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219798</v>
+        <v>2676</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595245</v>
+        <v>595213</v>
       </c>
       <c r="R36" t="n">
-        <v>6290215</v>
+        <v>6290222</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127736848</v>
+        <v>127736861</v>
       </c>
       <c r="B37" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595470</v>
+        <v>595396</v>
       </c>
       <c r="R37" t="n">
-        <v>6290237</v>
+        <v>6290191</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4361,10 +4361,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127736861</v>
+        <v>127736848</v>
       </c>
       <c r="B38" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>595396</v>
+        <v>595470</v>
       </c>
       <c r="R38" t="n">
-        <v>6290191</v>
+        <v>6290237</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4461,7 +4461,7 @@
         <v>127736832</v>
       </c>
       <c r="B39" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>127736724</v>
       </c>
       <c r="B40" t="n">
-        <v>98453</v>
+        <v>98546</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127736855</v>
+        <v>127736725</v>
       </c>
       <c r="B41" t="n">
-        <v>110572</v>
+        <v>98549</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4667,34 +4667,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>595472</v>
+        <v>595345</v>
       </c>
       <c r="R41" t="n">
-        <v>6290168</v>
+        <v>6290259</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4721,12 +4725,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4753,10 +4757,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127736725</v>
+        <v>127736855</v>
       </c>
       <c r="B42" t="n">
-        <v>98456</v>
+        <v>110665</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4764,38 +4768,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>595345</v>
+        <v>595472</v>
       </c>
       <c r="R42" t="n">
-        <v>6290259</v>
+        <v>6290168</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4857,7 +4857,7 @@
         <v>127736836</v>
       </c>
       <c r="B43" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>127736827</v>
       </c>
       <c r="B44" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>127736846</v>
       </c>
       <c r="B45" t="n">
-        <v>110572</v>
+        <v>110665</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>127736737</v>
       </c>
       <c r="B46" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>127736720</v>
       </c>
       <c r="B47" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>127736874</v>
       </c>
       <c r="B48" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>127736858</v>
       </c>
       <c r="B49" t="n">
-        <v>98501</v>
+        <v>98594</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>127736852</v>
       </c>
       <c r="B50" t="n">
-        <v>105428</v>
+        <v>105521</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>127736723</v>
       </c>
       <c r="B51" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>127736736</v>
       </c>
       <c r="B52" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>127736833</v>
       </c>
       <c r="B53" t="n">
-        <v>98500</v>
+        <v>98593</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5945,10 +5945,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127736866</v>
+        <v>127736727</v>
       </c>
       <c r="B54" t="n">
-        <v>110572</v>
+        <v>98549</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5956,34 +5956,38 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>595318</v>
+        <v>595482</v>
       </c>
       <c r="R54" t="n">
-        <v>6290207</v>
+        <v>6290215</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6010,12 +6014,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6042,10 +6046,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127736871</v>
+        <v>127736826</v>
       </c>
       <c r="B55" t="n">
-        <v>100660</v>
+        <v>98488</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6053,34 +6057,38 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>595263</v>
+        <v>595215</v>
       </c>
       <c r="R55" t="n">
-        <v>6290211</v>
+        <v>6290279</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6139,10 +6147,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127736727</v>
+        <v>127736726</v>
       </c>
       <c r="B56" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6178,10 +6186,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>595482</v>
+        <v>595419</v>
       </c>
       <c r="R56" t="n">
-        <v>6290215</v>
+        <v>6290207</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6240,10 +6248,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127736717</v>
+        <v>127736866</v>
       </c>
       <c r="B57" t="n">
-        <v>98456</v>
+        <v>110665</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6251,38 +6259,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>595312</v>
+        <v>595318</v>
       </c>
       <c r="R57" t="n">
-        <v>6290198</v>
+        <v>6290207</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6309,12 +6313,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6341,10 +6345,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127736826</v>
+        <v>127736717</v>
       </c>
       <c r="B58" t="n">
-        <v>98395</v>
+        <v>98549</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6352,26 +6356,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219790</v>
+        <v>219798</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6380,10 +6384,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>595215</v>
+        <v>595312</v>
       </c>
       <c r="R58" t="n">
-        <v>6290279</v>
+        <v>6290198</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6410,12 +6414,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6442,10 +6446,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127736726</v>
+        <v>127736871</v>
       </c>
       <c r="B59" t="n">
-        <v>98456</v>
+        <v>100753</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6453,38 +6457,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>595419</v>
+        <v>595263</v>
       </c>
       <c r="R59" t="n">
-        <v>6290207</v>
+        <v>6290211</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6511,12 +6511,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6546,7 +6546,7 @@
         <v>127736854</v>
       </c>
       <c r="B60" t="n">
-        <v>102982</v>
+        <v>103075</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>127736840</v>
       </c>
       <c r="B61" t="n">
-        <v>105428</v>
+        <v>105521</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>127736835</v>
       </c>
       <c r="B62" t="n">
-        <v>105428</v>
+        <v>105521</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>127736856</v>
       </c>
       <c r="B63" t="n">
-        <v>105428</v>
+        <v>105521</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>127736800</v>
       </c>
       <c r="B64" t="n">
-        <v>105428</v>
+        <v>105521</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7028,10 +7028,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127736838</v>
+        <v>127736716</v>
       </c>
       <c r="B65" t="n">
-        <v>100660</v>
+        <v>98549</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7039,34 +7039,38 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>595371</v>
+        <v>595320</v>
       </c>
       <c r="R65" t="n">
-        <v>6290254</v>
+        <v>6290193</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7093,12 +7097,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7125,10 +7129,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127736716</v>
+        <v>127736838</v>
       </c>
       <c r="B66" t="n">
-        <v>98456</v>
+        <v>100753</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7136,38 +7140,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>595320</v>
+        <v>595371</v>
       </c>
       <c r="R66" t="n">
-        <v>6290193</v>
+        <v>6290254</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7194,12 +7194,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7226,10 +7226,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127736853</v>
+        <v>127736870</v>
       </c>
       <c r="B67" t="n">
-        <v>100660</v>
+        <v>110665</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7237,21 +7237,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7261,10 +7261,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>595491</v>
+        <v>595272</v>
       </c>
       <c r="R67" t="n">
-        <v>6290172</v>
+        <v>6290205</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7323,10 +7323,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127736870</v>
+        <v>127736853</v>
       </c>
       <c r="B68" t="n">
-        <v>110572</v>
+        <v>100753</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7334,21 +7334,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7358,10 +7358,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>595272</v>
+        <v>595491</v>
       </c>
       <c r="R68" t="n">
-        <v>6290205</v>
+        <v>6290172</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127736718</v>
+        <v>127736863</v>
       </c>
       <c r="B69" t="n">
-        <v>98456</v>
+        <v>100753</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7431,38 +7431,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>595293</v>
+        <v>595354</v>
       </c>
       <c r="R69" t="n">
-        <v>6290204</v>
+        <v>6290194</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7489,12 +7485,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7521,10 +7517,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127736865</v>
+        <v>127736718</v>
       </c>
       <c r="B70" t="n">
-        <v>105428</v>
+        <v>98549</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7532,34 +7528,38 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221141</v>
+        <v>219798</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>595335</v>
+        <v>595293</v>
       </c>
       <c r="R70" t="n">
-        <v>6290212</v>
+        <v>6290204</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7586,12 +7586,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7618,10 +7618,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127736837</v>
+        <v>127736865</v>
       </c>
       <c r="B71" t="n">
-        <v>105428</v>
+        <v>105521</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7653,10 +7653,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>595371</v>
+        <v>595335</v>
       </c>
       <c r="R71" t="n">
-        <v>6290254</v>
+        <v>6290212</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7715,10 +7715,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127736863</v>
+        <v>127736837</v>
       </c>
       <c r="B72" t="n">
-        <v>100660</v>
+        <v>105521</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7726,21 +7726,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7750,10 +7750,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>595354</v>
+        <v>595371</v>
       </c>
       <c r="R72" t="n">
-        <v>6290194</v>
+        <v>6290254</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 21219-2023 artfynd.xlsx
+++ b/artfynd/A 21219-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AZ95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542137</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542117</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542961</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542082</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542104</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542112</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736715</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1445,6 +1485,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542119</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1547,6 +1592,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736733</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1658,6 +1708,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127051017</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1755,6 +1810,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542109</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1861,6 +1921,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77221027</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1972,6 +2037,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122753749</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2069,6 +2139,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736846</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2166,6 +2241,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736855</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2263,6 +2343,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736866</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2360,6 +2445,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736870</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2457,6 +2547,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736880</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2554,6 +2649,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736903</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2655,6 +2755,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736826</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2756,6 +2861,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736724</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2857,6 +2967,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736598</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2958,6 +3073,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736599</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3059,6 +3179,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736703</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3160,6 +3285,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736704</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3261,6 +3391,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736705</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3362,6 +3497,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736706</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3463,6 +3603,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736716</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3564,6 +3709,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736717</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3665,6 +3815,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736718</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3766,6 +3921,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736719</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3867,6 +4027,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736720</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3968,6 +4133,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736721</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4069,6 +4239,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736723</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4170,6 +4345,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736725</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4271,6 +4451,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736726</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4372,6 +4557,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736727</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4473,6 +4663,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736736</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4574,6 +4769,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736737</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4675,6 +4875,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736858</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4776,6 +4981,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736833</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4877,6 +5087,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736851</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4978,6 +5193,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736914</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5080,6 +5300,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122753994</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5177,6 +5402,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542115</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5274,6 +5504,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542133</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5371,6 +5606,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542134</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5468,6 +5708,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736795</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5565,6 +5810,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736797</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5662,6 +5912,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736800</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5759,6 +6014,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736812</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5856,6 +6116,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736825</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5953,6 +6218,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736831</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6050,6 +6320,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736835</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6147,6 +6422,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736837</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6244,6 +6524,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736840</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6341,6 +6626,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736844</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6438,6 +6728,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736852</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6535,6 +6830,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736856</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6632,6 +6932,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736860</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6729,6 +7034,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736865</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6826,6 +7136,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736872</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6923,6 +7238,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736902</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7020,6 +7340,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736854</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7126,6 +7451,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77221025</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7223,6 +7553,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542077</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7320,6 +7655,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542078</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7417,6 +7757,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542081</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7514,6 +7859,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542101</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7611,6 +7961,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542103</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7708,6 +8063,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542110</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7805,6 +8165,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542113</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7902,6 +8267,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542114</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7999,6 +8369,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542135</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8096,6 +8471,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542136</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8207,6 +8587,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122753750</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8304,6 +8689,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736827</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8401,6 +8791,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736832</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8498,6 +8893,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736836</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8595,6 +8995,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736838</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8692,6 +9097,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736842</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8789,6 +9199,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736848</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8886,6 +9301,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736853</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8983,6 +9403,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736857</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9080,6 +9505,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736861</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9177,6 +9607,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736863</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9274,6 +9709,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736867</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9371,6 +9811,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736871</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9468,6 +9913,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736874</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9565,6 +10015,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736877</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9662,6 +10117,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736879</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9759,6 +10219,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736915</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9860,6 +10325,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736859</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9957,8 +10427,109 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542083</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>